--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Berni\Desktop\coleccion-tarjetas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2651AECB-AD57-4656-AE4E-1AE220F42264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30551A5E-FBE6-4698-BB59-D9BFAF218894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="47025" yWindow="0" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
   </bookViews>
@@ -10272,7 +10272,7 @@
         <v>10</v>
       </c>
       <c r="D243" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E243" t="s">
         <v>522</v>
@@ -10470,7 +10470,7 @@
         <v>10</v>
       </c>
       <c r="D249" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E249" t="s">
         <v>529</v>
@@ -10503,7 +10503,7 @@
         <v>10</v>
       </c>
       <c r="D250" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E250" t="s">
         <v>530</v>
@@ -10536,7 +10536,7 @@
         <v>10</v>
       </c>
       <c r="D251" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E251" t="s">
         <v>531</v>

--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Berni\Desktop\coleccion-tarjetas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30551A5E-FBE6-4698-BB59-D9BFAF218894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68738E65-FD6F-4F9B-956B-E6AE9204C9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47025" yWindow="0" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
+    <workbookView xWindow="47370" yWindow="345" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -12518,7 +12518,7 @@
         <v>10</v>
       </c>
       <c r="D315" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E315" t="s">
         <v>683</v>

--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Berni\Desktop\coleccion-tarjetas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68738E65-FD6F-4F9B-956B-E6AE9204C9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F9C688-CDB9-4AAD-BB4F-DBA52A1F1AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47370" yWindow="345" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
+    <workbookView xWindow="50880" yWindow="330" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="749">
   <si>
     <t>id</t>
   </si>
@@ -2157,6 +2157,132 @@
   </si>
   <si>
     <t>2021-22 Obsidian  Rookie Dual Relic Autograph Auto /35</t>
+  </si>
+  <si>
+    <t>Card-338</t>
+  </si>
+  <si>
+    <t>Card-339</t>
+  </si>
+  <si>
+    <t>Card-340</t>
+  </si>
+  <si>
+    <t>Card-341</t>
+  </si>
+  <si>
+    <t>Card-342</t>
+  </si>
+  <si>
+    <t>Card-343</t>
+  </si>
+  <si>
+    <t>Card-344</t>
+  </si>
+  <si>
+    <t>Card-345</t>
+  </si>
+  <si>
+    <t>Card-346</t>
+  </si>
+  <si>
+    <t>Card-347</t>
+  </si>
+  <si>
+    <t>Card-348</t>
+  </si>
+  <si>
+    <t>Card-349</t>
+  </si>
+  <si>
+    <t>Card-350</t>
+  </si>
+  <si>
+    <t>Card-351</t>
+  </si>
+  <si>
+    <t>Card-352</t>
+  </si>
+  <si>
+    <t>Card-353</t>
+  </si>
+  <si>
+    <t>Card-354</t>
+  </si>
+  <si>
+    <t>Card-355</t>
+  </si>
+  <si>
+    <t>Card-356</t>
+  </si>
+  <si>
+    <t>Card-357</t>
+  </si>
+  <si>
+    <t>Card-358</t>
+  </si>
+  <si>
+    <t>2007 Panini LaLiga Mega Cracks #387 PSA 6.5 EXMT+</t>
+  </si>
+  <si>
+    <t>2007 Panini Copa America Venezuela #200 PSA 8 NM-MT</t>
+  </si>
+  <si>
+    <t>2019 Panini La Liga Megacracks Elite  #371 PSA 8 NM-MT</t>
+  </si>
+  <si>
+    <t>2020 Panini La Liga Megacracks Edicion Limitada PSA 9 MINT</t>
+  </si>
+  <si>
+    <t>2021 Panini FIFA 365  #341 PSA 9 MINT</t>
+  </si>
+  <si>
+    <t>2024 Panini Copa America Extra Sticker Brazil Bronze  CGC AUTH</t>
+  </si>
+  <si>
+    <t>1990 Panini World Cup #128 SGC 4 VGEX</t>
+  </si>
+  <si>
+    <t>2009 Upper Deck First Edition ROOKIE #196 BGS 9 MINT</t>
+  </si>
+  <si>
+    <t>2014 Panini Prizm World Cup #12 PSA 9 MINT</t>
+  </si>
+  <si>
+    <t>2022 FansMall Light Argentina Emerald Lionel Scaloni AUTO /5 #CO-LS</t>
+  </si>
+  <si>
+    <t>1986 Panini Mexico '86  #84 PSA 6 EXMT</t>
+  </si>
+  <si>
+    <t>2022 FansMall Light Argentina Blue ROOKIE AUTO /99 MBA AUTH</t>
+  </si>
+  <si>
+    <t>2021 Panini Futbol Argentino ROOKIE #373 MBA AUTH</t>
+  </si>
+  <si>
+    <t>1979 Crack Super Futbol #58 BVG 3 VG</t>
+  </si>
+  <si>
+    <t>2003 Bowman Gold  ROOKIE #123 BGS 7 NRMT</t>
+  </si>
+  <si>
+    <t>2005 SPx SPxcitement Veterans /999 #XCV3 BGS 8 NM-MT</t>
+  </si>
+  <si>
+    <t>2003 Upper Deck Honor Roll Popular Acclaim ROOKIE #PA7 BGS 8 NM-MT</t>
+  </si>
+  <si>
+    <t>1996 Ultra Basketball  ROOKIE #52 BGS 8.5 NM-MT+</t>
+  </si>
+  <si>
+    <t>1996 Stadium Club Showcase ROOKIE #RS11 BGS 8.5 NM-MT+</t>
+  </si>
+  <si>
+    <t>1997 Skybox Z-Force Star Gazing  #2 BGS 9 MINT</t>
+  </si>
+  <si>
+    <t>Pack sealed Panini Sticker Pack Fifa World Cup Russia 2018</t>
   </si>
 </sst>
 </file>
@@ -2534,7 +2660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DAA126C-D60B-4EC0-8FDE-28B90D0445C8}">
-  <dimension ref="A1:N338"/>
+  <dimension ref="A1:N359"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="36.140625" customWidth="1"/>
@@ -2591,7 +2717,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -2630,7 +2756,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -2669,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -2711,7 +2837,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -2751,7 +2877,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -2794,7 +2920,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
@@ -2834,7 +2960,7 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
@@ -2877,7 +3003,7 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
@@ -2917,7 +3043,7 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
@@ -2960,7 +3086,7 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
@@ -2997,7 +3123,7 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
@@ -3040,7 +3166,7 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
@@ -3080,7 +3206,7 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
@@ -3120,7 +3246,7 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
@@ -3157,7 +3283,7 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D16" t="s">
         <v>6</v>
@@ -3200,7 +3326,7 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D17" t="s">
         <v>8</v>
@@ -3237,7 +3363,7 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>
@@ -3277,7 +3403,7 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D19" t="s">
         <v>6</v>
@@ -3317,7 +3443,7 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
         <v>6</v>
@@ -3357,7 +3483,7 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D21" t="s">
         <v>6</v>
@@ -3397,7 +3523,7 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D22" t="s">
         <v>6</v>
@@ -3437,7 +3563,7 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D23" t="s">
         <v>6</v>
@@ -3477,7 +3603,7 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D24" t="s">
         <v>8</v>
@@ -3514,7 +3640,7 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D25" t="s">
         <v>8</v>
@@ -3551,7 +3677,7 @@
         <v>25</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D26" t="s">
         <v>8</v>
@@ -3588,7 +3714,7 @@
         <v>26</v>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
@@ -3625,7 +3751,7 @@
         <v>27</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
@@ -3662,7 +3788,7 @@
         <v>28</v>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D29" t="s">
         <v>8</v>
@@ -3699,7 +3825,7 @@
         <v>29</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D30" t="s">
         <v>6</v>
@@ -3736,7 +3862,7 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D31" t="s">
         <v>6</v>
@@ -3776,7 +3902,7 @@
         <v>31</v>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D32" t="s">
         <v>6</v>
@@ -3813,7 +3939,7 @@
         <v>32</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D33" t="s">
         <v>6</v>
@@ -3850,7 +3976,7 @@
         <v>33</v>
       </c>
       <c r="C34">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D34" t="s">
         <v>6</v>
@@ -3887,7 +4013,7 @@
         <v>34</v>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D35" t="s">
         <v>8</v>
@@ -3924,7 +4050,7 @@
         <v>35</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D36" t="s">
         <v>8</v>
@@ -3961,7 +4087,7 @@
         <v>36</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D37" t="s">
         <v>8</v>
@@ -3998,7 +4124,7 @@
         <v>37</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D38" t="s">
         <v>8</v>
@@ -4035,7 +4161,7 @@
         <v>38</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D39" t="s">
         <v>6</v>
@@ -4072,7 +4198,7 @@
         <v>39</v>
       </c>
       <c r="C40">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D40" t="s">
         <v>6</v>
@@ -4112,7 +4238,7 @@
         <v>40</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D41" t="s">
         <v>6</v>
@@ -4149,7 +4275,7 @@
         <v>41</v>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D42" t="s">
         <v>6</v>
@@ -4182,7 +4308,7 @@
         <v>42</v>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D43" t="s">
         <v>6</v>
@@ -4215,7 +4341,7 @@
         <v>43</v>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D44" t="s">
         <v>6</v>
@@ -4248,7 +4374,7 @@
         <v>44</v>
       </c>
       <c r="C45">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D45" t="s">
         <v>6</v>
@@ -4281,7 +4407,7 @@
         <v>45</v>
       </c>
       <c r="C46">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D46" t="s">
         <v>6</v>
@@ -4314,7 +4440,7 @@
         <v>46</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D47" t="s">
         <v>8</v>
@@ -4344,7 +4470,7 @@
         <v>47</v>
       </c>
       <c r="C48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D48" t="s">
         <v>8</v>
@@ -4374,7 +4500,7 @@
         <v>48</v>
       </c>
       <c r="C49">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D49" t="s">
         <v>8</v>
@@ -4404,7 +4530,7 @@
         <v>49</v>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D50" t="s">
         <v>8</v>
@@ -4434,7 +4560,7 @@
         <v>50</v>
       </c>
       <c r="C51">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D51" t="s">
         <v>8</v>
@@ -4464,7 +4590,7 @@
         <v>51</v>
       </c>
       <c r="C52">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D52" t="s">
         <v>8</v>
@@ -4494,7 +4620,7 @@
         <v>52</v>
       </c>
       <c r="C53">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D53" t="s">
         <v>8</v>
@@ -4524,7 +4650,7 @@
         <v>53</v>
       </c>
       <c r="C54">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D54" t="s">
         <v>8</v>
@@ -4554,7 +4680,7 @@
         <v>54</v>
       </c>
       <c r="C55">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D55" t="s">
         <v>8</v>
@@ -4584,7 +4710,7 @@
         <v>55</v>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D56" t="s">
         <v>8</v>
@@ -4614,7 +4740,7 @@
         <v>56</v>
       </c>
       <c r="C57">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D57" t="s">
         <v>8</v>
@@ -4644,7 +4770,7 @@
         <v>57</v>
       </c>
       <c r="C58">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D58" t="s">
         <v>8</v>
@@ -4674,7 +4800,7 @@
         <v>58</v>
       </c>
       <c r="C59">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D59" t="s">
         <v>8</v>
@@ -4704,7 +4830,7 @@
         <v>59</v>
       </c>
       <c r="C60">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D60" t="s">
         <v>8</v>
@@ -4734,7 +4860,7 @@
         <v>60</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D61" t="s">
         <v>8</v>
@@ -4767,7 +4893,7 @@
         <v>61</v>
       </c>
       <c r="C62">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D62" t="s">
         <v>8</v>
@@ -4797,7 +4923,7 @@
         <v>62</v>
       </c>
       <c r="C63">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D63" t="s">
         <v>8</v>
@@ -4827,7 +4953,7 @@
         <v>63</v>
       </c>
       <c r="C64">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D64" t="s">
         <v>8</v>
@@ -4857,7 +4983,7 @@
         <v>64</v>
       </c>
       <c r="C65">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D65" t="s">
         <v>8</v>
@@ -4887,7 +5013,7 @@
         <v>65</v>
       </c>
       <c r="C66">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D66" t="s">
         <v>8</v>
@@ -4917,7 +5043,7 @@
         <v>66</v>
       </c>
       <c r="C67">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D67" t="s">
         <v>8</v>
@@ -4947,7 +5073,7 @@
         <v>67</v>
       </c>
       <c r="C68">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D68" t="s">
         <v>8</v>
@@ -4977,7 +5103,7 @@
         <v>68</v>
       </c>
       <c r="C69">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D69" t="s">
         <v>8</v>
@@ -5007,7 +5133,7 @@
         <v>69</v>
       </c>
       <c r="C70">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D70" t="s">
         <v>8</v>
@@ -5037,7 +5163,7 @@
         <v>70</v>
       </c>
       <c r="C71">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D71" t="s">
         <v>8</v>
@@ -5067,7 +5193,7 @@
         <v>71</v>
       </c>
       <c r="C72">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D72" t="s">
         <v>8</v>
@@ -5097,7 +5223,7 @@
         <v>72</v>
       </c>
       <c r="C73">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D73" t="s">
         <v>8</v>
@@ -5127,7 +5253,7 @@
         <v>73</v>
       </c>
       <c r="C74">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D74" t="s">
         <v>8</v>
@@ -5157,7 +5283,7 @@
         <v>74</v>
       </c>
       <c r="C75">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D75" t="s">
         <v>8</v>
@@ -5187,7 +5313,7 @@
         <v>75</v>
       </c>
       <c r="C76">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D76" t="s">
         <v>8</v>
@@ -5217,7 +5343,7 @@
         <v>76</v>
       </c>
       <c r="C77">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D77" t="s">
         <v>8</v>
@@ -5247,7 +5373,7 @@
         <v>77</v>
       </c>
       <c r="C78">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D78" t="s">
         <v>8</v>
@@ -5277,7 +5403,7 @@
         <v>78</v>
       </c>
       <c r="C79">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D79" t="s">
         <v>8</v>
@@ -5307,7 +5433,7 @@
         <v>79</v>
       </c>
       <c r="C80">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D80" t="s">
         <v>8</v>
@@ -5337,7 +5463,7 @@
         <v>80</v>
       </c>
       <c r="C81">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D81" t="s">
         <v>8</v>
@@ -5367,7 +5493,7 @@
         <v>81</v>
       </c>
       <c r="C82">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D82" t="s">
         <v>8</v>
@@ -5397,7 +5523,7 @@
         <v>82</v>
       </c>
       <c r="C83">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D83" t="s">
         <v>8</v>
@@ -5427,7 +5553,7 @@
         <v>83</v>
       </c>
       <c r="C84">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D84" t="s">
         <v>8</v>
@@ -5457,7 +5583,7 @@
         <v>84</v>
       </c>
       <c r="C85">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D85" t="s">
         <v>8</v>
@@ -5487,7 +5613,7 @@
         <v>85</v>
       </c>
       <c r="C86">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D86" t="s">
         <v>8</v>
@@ -5517,7 +5643,7 @@
         <v>86</v>
       </c>
       <c r="C87">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D87" t="s">
         <v>6</v>
@@ -5547,7 +5673,7 @@
         <v>87</v>
       </c>
       <c r="C88">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D88" t="s">
         <v>6</v>
@@ -5577,7 +5703,7 @@
         <v>88</v>
       </c>
       <c r="C89">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D89" t="s">
         <v>6</v>
@@ -5607,7 +5733,7 @@
         <v>89</v>
       </c>
       <c r="C90">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D90" t="s">
         <v>8</v>
@@ -5637,7 +5763,7 @@
         <v>90</v>
       </c>
       <c r="C91">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D91" t="s">
         <v>8</v>
@@ -5670,7 +5796,7 @@
         <v>91</v>
       </c>
       <c r="C92">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D92" t="s">
         <v>6</v>
@@ -5700,7 +5826,7 @@
         <v>92</v>
       </c>
       <c r="C93">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D93" t="s">
         <v>8</v>
@@ -5730,7 +5856,7 @@
         <v>93</v>
       </c>
       <c r="C94">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D94" t="s">
         <v>8</v>
@@ -5760,7 +5886,7 @@
         <v>94</v>
       </c>
       <c r="C95">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D95" t="s">
         <v>8</v>
@@ -5790,7 +5916,7 @@
         <v>95</v>
       </c>
       <c r="C96">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D96" t="s">
         <v>8</v>
@@ -5823,7 +5949,7 @@
         <v>96</v>
       </c>
       <c r="C97">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D97" t="s">
         <v>8</v>
@@ -5856,7 +5982,7 @@
         <v>97</v>
       </c>
       <c r="C98">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D98" t="s">
         <v>8</v>
@@ -5889,7 +6015,7 @@
         <v>98</v>
       </c>
       <c r="C99">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D99" t="s">
         <v>8</v>
@@ -5922,7 +6048,7 @@
         <v>99</v>
       </c>
       <c r="C100">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D100" t="s">
         <v>8</v>
@@ -5952,7 +6078,7 @@
         <v>100</v>
       </c>
       <c r="C101">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D101" t="s">
         <v>8</v>
@@ -5982,7 +6108,7 @@
         <v>101</v>
       </c>
       <c r="C102">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D102" t="s">
         <v>8</v>
@@ -6012,7 +6138,7 @@
         <v>102</v>
       </c>
       <c r="C103">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D103" t="s">
         <v>8</v>
@@ -6042,7 +6168,7 @@
         <v>103</v>
       </c>
       <c r="C104">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D104" t="s">
         <v>8</v>
@@ -6072,7 +6198,7 @@
         <v>104</v>
       </c>
       <c r="C105">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D105" t="s">
         <v>8</v>
@@ -6102,7 +6228,7 @@
         <v>105</v>
       </c>
       <c r="C106">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D106" t="s">
         <v>8</v>
@@ -6132,7 +6258,7 @@
         <v>106</v>
       </c>
       <c r="C107">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D107" t="s">
         <v>8</v>
@@ -6162,7 +6288,7 @@
         <v>107</v>
       </c>
       <c r="C108">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D108" t="s">
         <v>8</v>
@@ -6192,7 +6318,7 @@
         <v>108</v>
       </c>
       <c r="C109">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D109" t="s">
         <v>8</v>
@@ -6222,7 +6348,7 @@
         <v>109</v>
       </c>
       <c r="C110">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D110" t="s">
         <v>8</v>
@@ -6252,7 +6378,7 @@
         <v>110</v>
       </c>
       <c r="C111">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D111" t="s">
         <v>8</v>
@@ -6282,7 +6408,7 @@
         <v>111</v>
       </c>
       <c r="C112">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D112" t="s">
         <v>8</v>
@@ -6312,7 +6438,7 @@
         <v>112</v>
       </c>
       <c r="C113">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D113" t="s">
         <v>6</v>
@@ -6345,7 +6471,7 @@
         <v>113</v>
       </c>
       <c r="C114">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D114" t="s">
         <v>8</v>
@@ -6375,7 +6501,7 @@
         <v>114</v>
       </c>
       <c r="C115">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D115" t="s">
         <v>8</v>
@@ -6405,7 +6531,7 @@
         <v>115</v>
       </c>
       <c r="C116">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D116" t="s">
         <v>8</v>
@@ -6435,7 +6561,7 @@
         <v>116</v>
       </c>
       <c r="C117">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D117" t="s">
         <v>8</v>
@@ -6465,7 +6591,7 @@
         <v>117</v>
       </c>
       <c r="C118">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D118" t="s">
         <v>8</v>
@@ -6495,7 +6621,7 @@
         <v>118</v>
       </c>
       <c r="C119">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D119" t="s">
         <v>8</v>
@@ -6525,7 +6651,7 @@
         <v>119</v>
       </c>
       <c r="C120">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D120" t="s">
         <v>8</v>
@@ -6555,7 +6681,7 @@
         <v>120</v>
       </c>
       <c r="C121">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D121" t="s">
         <v>8</v>
@@ -6585,7 +6711,7 @@
         <v>121</v>
       </c>
       <c r="C122">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D122" t="s">
         <v>8</v>
@@ -6615,7 +6741,7 @@
         <v>122</v>
       </c>
       <c r="C123">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D123" t="s">
         <v>8</v>
@@ -6645,7 +6771,7 @@
         <v>123</v>
       </c>
       <c r="C124">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D124" t="s">
         <v>8</v>
@@ -6675,7 +6801,7 @@
         <v>124</v>
       </c>
       <c r="C125">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D125" t="s">
         <v>8</v>
@@ -6705,7 +6831,7 @@
         <v>125</v>
       </c>
       <c r="C126">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D126" t="s">
         <v>8</v>
@@ -6735,7 +6861,7 @@
         <v>126</v>
       </c>
       <c r="C127">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D127" t="s">
         <v>8</v>
@@ -6765,7 +6891,7 @@
         <v>127</v>
       </c>
       <c r="C128">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D128" t="s">
         <v>8</v>
@@ -6795,7 +6921,7 @@
         <v>128</v>
       </c>
       <c r="C129">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D129" t="s">
         <v>8</v>
@@ -6825,7 +6951,7 @@
         <v>129</v>
       </c>
       <c r="C130">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D130" t="s">
         <v>8</v>
@@ -6855,7 +6981,7 @@
         <v>130</v>
       </c>
       <c r="C131">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D131" t="s">
         <v>8</v>
@@ -6885,7 +7011,7 @@
         <v>131</v>
       </c>
       <c r="C132">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D132" t="s">
         <v>8</v>
@@ -6915,7 +7041,7 @@
         <v>132</v>
       </c>
       <c r="C133">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D133" t="s">
         <v>8</v>
@@ -6945,7 +7071,7 @@
         <v>133</v>
       </c>
       <c r="C134">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D134" t="s">
         <v>8</v>
@@ -6975,7 +7101,7 @@
         <v>134</v>
       </c>
       <c r="C135">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D135" t="s">
         <v>8</v>
@@ -7005,7 +7131,7 @@
         <v>135</v>
       </c>
       <c r="C136">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D136" t="s">
         <v>8</v>
@@ -7035,7 +7161,7 @@
         <v>136</v>
       </c>
       <c r="C137">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D137" t="s">
         <v>8</v>
@@ -7065,7 +7191,7 @@
         <v>137</v>
       </c>
       <c r="C138">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D138" t="s">
         <v>8</v>
@@ -7095,7 +7221,7 @@
         <v>138</v>
       </c>
       <c r="C139">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D139" t="s">
         <v>8</v>
@@ -7125,7 +7251,7 @@
         <v>139</v>
       </c>
       <c r="C140">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D140" t="s">
         <v>8</v>
@@ -7155,7 +7281,7 @@
         <v>140</v>
       </c>
       <c r="C141">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D141" t="s">
         <v>8</v>
@@ -7185,7 +7311,7 @@
         <v>141</v>
       </c>
       <c r="C142">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D142" t="s">
         <v>8</v>
@@ -7215,7 +7341,7 @@
         <v>142</v>
       </c>
       <c r="C143">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D143" t="s">
         <v>8</v>
@@ -7245,7 +7371,7 @@
         <v>143</v>
       </c>
       <c r="C144">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D144" t="s">
         <v>8</v>
@@ -7275,7 +7401,7 @@
         <v>144</v>
       </c>
       <c r="C145">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D145" t="s">
         <v>8</v>
@@ -7305,7 +7431,7 @@
         <v>145</v>
       </c>
       <c r="C146">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D146" t="s">
         <v>8</v>
@@ -7335,7 +7461,7 @@
         <v>146</v>
       </c>
       <c r="C147">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D147" t="s">
         <v>8</v>
@@ -7365,7 +7491,7 @@
         <v>147</v>
       </c>
       <c r="C148">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D148" t="s">
         <v>8</v>
@@ -7395,7 +7521,7 @@
         <v>148</v>
       </c>
       <c r="C149">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D149" t="s">
         <v>8</v>
@@ -7425,7 +7551,7 @@
         <v>149</v>
       </c>
       <c r="C150">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D150" t="s">
         <v>8</v>
@@ -7455,7 +7581,7 @@
         <v>150</v>
       </c>
       <c r="C151">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D151" t="s">
         <v>8</v>
@@ -7485,7 +7611,7 @@
         <v>151</v>
       </c>
       <c r="C152">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D152" t="s">
         <v>8</v>
@@ -7515,7 +7641,7 @@
         <v>152</v>
       </c>
       <c r="C153">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D153" t="s">
         <v>8</v>
@@ -7545,7 +7671,7 @@
         <v>153</v>
       </c>
       <c r="C154">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D154" t="s">
         <v>8</v>
@@ -7575,7 +7701,7 @@
         <v>154</v>
       </c>
       <c r="C155">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D155" t="s">
         <v>8</v>
@@ -7605,7 +7731,7 @@
         <v>155</v>
       </c>
       <c r="C156">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D156" t="s">
         <v>8</v>
@@ -7635,7 +7761,7 @@
         <v>156</v>
       </c>
       <c r="C157">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D157" t="s">
         <v>8</v>
@@ -7665,7 +7791,7 @@
         <v>157</v>
       </c>
       <c r="C158">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D158" t="s">
         <v>8</v>
@@ -7695,7 +7821,7 @@
         <v>158</v>
       </c>
       <c r="C159">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D159" t="s">
         <v>8</v>
@@ -7725,7 +7851,7 @@
         <v>159</v>
       </c>
       <c r="C160">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D160" t="s">
         <v>8</v>
@@ -7755,7 +7881,7 @@
         <v>160</v>
       </c>
       <c r="C161">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D161" t="s">
         <v>8</v>
@@ -7785,7 +7911,7 @@
         <v>161</v>
       </c>
       <c r="C162">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D162" t="s">
         <v>6</v>
@@ -7815,7 +7941,7 @@
         <v>162</v>
       </c>
       <c r="C163">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D163" t="s">
         <v>8</v>
@@ -7845,7 +7971,7 @@
         <v>163</v>
       </c>
       <c r="C164">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D164" t="s">
         <v>8</v>
@@ -7875,7 +8001,7 @@
         <v>164</v>
       </c>
       <c r="C165">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D165" t="s">
         <v>8</v>
@@ -7905,7 +8031,7 @@
         <v>165</v>
       </c>
       <c r="C166">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D166" t="s">
         <v>8</v>
@@ -7935,7 +8061,7 @@
         <v>166</v>
       </c>
       <c r="C167">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D167" t="s">
         <v>8</v>
@@ -7965,7 +8091,7 @@
         <v>167</v>
       </c>
       <c r="C168">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D168" t="s">
         <v>8</v>
@@ -7995,7 +8121,7 @@
         <v>168</v>
       </c>
       <c r="C169">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D169" t="s">
         <v>8</v>
@@ -8025,7 +8151,7 @@
         <v>169</v>
       </c>
       <c r="C170">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D170" t="s">
         <v>8</v>
@@ -8055,7 +8181,7 @@
         <v>170</v>
       </c>
       <c r="C171">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D171" t="s">
         <v>8</v>
@@ -8085,7 +8211,7 @@
         <v>171</v>
       </c>
       <c r="C172">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D172" t="s">
         <v>8</v>
@@ -8115,7 +8241,7 @@
         <v>172</v>
       </c>
       <c r="C173">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D173" t="s">
         <v>8</v>
@@ -8145,7 +8271,7 @@
         <v>173</v>
       </c>
       <c r="C174">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D174" t="s">
         <v>6</v>
@@ -8175,7 +8301,7 @@
         <v>174</v>
       </c>
       <c r="C175">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D175" t="s">
         <v>8</v>
@@ -8205,7 +8331,7 @@
         <v>175</v>
       </c>
       <c r="C176">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D176" t="s">
         <v>8</v>
@@ -8235,7 +8361,7 @@
         <v>176</v>
       </c>
       <c r="C177">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D177" t="s">
         <v>8</v>
@@ -8265,7 +8391,7 @@
         <v>177</v>
       </c>
       <c r="C178">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D178" t="s">
         <v>8</v>
@@ -8295,7 +8421,7 @@
         <v>178</v>
       </c>
       <c r="C179">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D179" t="s">
         <v>8</v>
@@ -8325,7 +8451,7 @@
         <v>179</v>
       </c>
       <c r="C180">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D180" t="s">
         <v>8</v>
@@ -8355,7 +8481,7 @@
         <v>180</v>
       </c>
       <c r="C181">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D181" t="s">
         <v>6</v>
@@ -8388,7 +8514,7 @@
         <v>181</v>
       </c>
       <c r="C182">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D182" t="s">
         <v>6</v>
@@ -8421,7 +8547,7 @@
         <v>182</v>
       </c>
       <c r="C183">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D183" t="s">
         <v>6</v>
@@ -8451,7 +8577,7 @@
         <v>183</v>
       </c>
       <c r="C184">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D184" t="s">
         <v>6</v>
@@ -8484,7 +8610,7 @@
         <v>184</v>
       </c>
       <c r="C185">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D185" t="s">
         <v>6</v>
@@ -8517,7 +8643,7 @@
         <v>185</v>
       </c>
       <c r="C186">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D186" t="s">
         <v>6</v>
@@ -8550,7 +8676,7 @@
         <v>186</v>
       </c>
       <c r="C187">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D187" t="s">
         <v>6</v>
@@ -8583,7 +8709,7 @@
         <v>187</v>
       </c>
       <c r="C188">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D188" t="s">
         <v>6</v>
@@ -8616,7 +8742,7 @@
         <v>188</v>
       </c>
       <c r="C189">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D189" t="s">
         <v>6</v>
@@ -8646,7 +8772,7 @@
         <v>189</v>
       </c>
       <c r="C190">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D190" t="s">
         <v>6</v>
@@ -8676,7 +8802,7 @@
         <v>190</v>
       </c>
       <c r="C191">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D191" t="s">
         <v>6</v>
@@ -8706,7 +8832,7 @@
         <v>191</v>
       </c>
       <c r="C192">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D192" t="s">
         <v>6</v>
@@ -8736,7 +8862,7 @@
         <v>192</v>
       </c>
       <c r="C193">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D193" t="s">
         <v>6</v>
@@ -8766,7 +8892,7 @@
         <v>193</v>
       </c>
       <c r="C194">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D194" t="s">
         <v>6</v>
@@ -8796,7 +8922,7 @@
         <v>194</v>
       </c>
       <c r="C195">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D195" t="s">
         <v>6</v>
@@ -8826,7 +8952,7 @@
         <v>195</v>
       </c>
       <c r="C196">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D196" t="s">
         <v>6</v>
@@ -8856,7 +8982,7 @@
         <v>196</v>
       </c>
       <c r="C197">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D197" t="s">
         <v>6</v>
@@ -8886,7 +9012,7 @@
         <v>197</v>
       </c>
       <c r="C198">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D198" t="s">
         <v>6</v>
@@ -8916,7 +9042,7 @@
         <v>198</v>
       </c>
       <c r="C199">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D199" t="s">
         <v>6</v>
@@ -8946,7 +9072,7 @@
         <v>199</v>
       </c>
       <c r="C200">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D200" t="s">
         <v>6</v>
@@ -8976,7 +9102,7 @@
         <v>200</v>
       </c>
       <c r="C201">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D201" t="s">
         <v>6</v>
@@ -9006,7 +9132,7 @@
         <v>201</v>
       </c>
       <c r="C202">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D202" t="s">
         <v>6</v>
@@ -9036,7 +9162,7 @@
         <v>202</v>
       </c>
       <c r="C203">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D203" t="s">
         <v>6</v>
@@ -9066,7 +9192,7 @@
         <v>203</v>
       </c>
       <c r="C204">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D204" t="s">
         <v>6</v>
@@ -9096,7 +9222,7 @@
         <v>204</v>
       </c>
       <c r="C205">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D205" t="s">
         <v>6</v>
@@ -9126,7 +9252,7 @@
         <v>205</v>
       </c>
       <c r="C206">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D206" t="s">
         <v>6</v>
@@ -9156,7 +9282,7 @@
         <v>206</v>
       </c>
       <c r="C207">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D207" t="s">
         <v>6</v>
@@ -9186,7 +9312,7 @@
         <v>207</v>
       </c>
       <c r="C208">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D208" t="s">
         <v>6</v>
@@ -9216,7 +9342,7 @@
         <v>208</v>
       </c>
       <c r="C209">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D209" t="s">
         <v>6</v>
@@ -9249,7 +9375,7 @@
         <v>209</v>
       </c>
       <c r="C210">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D210" t="s">
         <v>6</v>
@@ -9279,7 +9405,7 @@
         <v>210</v>
       </c>
       <c r="C211">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D211" t="s">
         <v>6</v>
@@ -9309,7 +9435,7 @@
         <v>211</v>
       </c>
       <c r="C212">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D212" t="s">
         <v>6</v>
@@ -9342,7 +9468,7 @@
         <v>212</v>
       </c>
       <c r="C213">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D213" t="s">
         <v>6</v>
@@ -9372,7 +9498,7 @@
         <v>213</v>
       </c>
       <c r="C214">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D214" t="s">
         <v>6</v>
@@ -9405,7 +9531,7 @@
         <v>214</v>
       </c>
       <c r="C215">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D215" t="s">
         <v>6</v>
@@ -9435,7 +9561,7 @@
         <v>215</v>
       </c>
       <c r="C216">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D216" t="s">
         <v>6</v>
@@ -9465,7 +9591,7 @@
         <v>216</v>
       </c>
       <c r="C217">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D217" t="s">
         <v>6</v>
@@ -9495,7 +9621,7 @@
         <v>217</v>
       </c>
       <c r="C218">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D218" t="s">
         <v>6</v>
@@ -9528,7 +9654,7 @@
         <v>218</v>
       </c>
       <c r="C219">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D219" t="s">
         <v>6</v>
@@ -9561,7 +9687,7 @@
         <v>219</v>
       </c>
       <c r="C220">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D220" t="s">
         <v>6</v>
@@ -9591,7 +9717,7 @@
         <v>220</v>
       </c>
       <c r="C221">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D221" t="s">
         <v>6</v>
@@ -9624,7 +9750,7 @@
         <v>221</v>
       </c>
       <c r="C222">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D222" t="s">
         <v>6</v>
@@ -9657,7 +9783,7 @@
         <v>222</v>
       </c>
       <c r="C223">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D223" t="s">
         <v>6</v>
@@ -9687,7 +9813,7 @@
         <v>223</v>
       </c>
       <c r="C224">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D224" t="s">
         <v>6</v>
@@ -9720,7 +9846,7 @@
         <v>224</v>
       </c>
       <c r="C225">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D225" t="s">
         <v>6</v>
@@ -9750,7 +9876,7 @@
         <v>225</v>
       </c>
       <c r="C226">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D226" t="s">
         <v>8</v>
@@ -9780,7 +9906,7 @@
         <v>226</v>
       </c>
       <c r="C227">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D227" t="s">
         <v>6</v>
@@ -9810,7 +9936,7 @@
         <v>227</v>
       </c>
       <c r="C228">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D228" t="s">
         <v>6</v>
@@ -9840,7 +9966,7 @@
         <v>228</v>
       </c>
       <c r="C229">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D229" t="s">
         <v>6</v>
@@ -9870,7 +9996,7 @@
         <v>229</v>
       </c>
       <c r="C230">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D230" t="s">
         <v>6</v>
@@ -9900,7 +10026,7 @@
         <v>230</v>
       </c>
       <c r="C231">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D231" t="s">
         <v>6</v>
@@ -9930,7 +10056,7 @@
         <v>231</v>
       </c>
       <c r="C232">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D232" t="s">
         <v>6</v>
@@ -9960,7 +10086,7 @@
         <v>232</v>
       </c>
       <c r="C233">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D233" t="s">
         <v>6</v>
@@ -9990,7 +10116,7 @@
         <v>233</v>
       </c>
       <c r="C234">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D234" t="s">
         <v>6</v>
@@ -10020,7 +10146,7 @@
         <v>234</v>
       </c>
       <c r="C235">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D235" t="s">
         <v>6</v>
@@ -10050,7 +10176,7 @@
         <v>235</v>
       </c>
       <c r="C236">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D236" t="s">
         <v>6</v>
@@ -10083,7 +10209,7 @@
         <v>236</v>
       </c>
       <c r="C237">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D237" t="s">
         <v>6</v>
@@ -10113,7 +10239,7 @@
         <v>237</v>
       </c>
       <c r="C238">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D238" t="s">
         <v>6</v>
@@ -10143,7 +10269,7 @@
         <v>238</v>
       </c>
       <c r="C239">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D239" t="s">
         <v>6</v>
@@ -10176,7 +10302,7 @@
         <v>239</v>
       </c>
       <c r="C240">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D240" t="s">
         <v>6</v>
@@ -10206,7 +10332,7 @@
         <v>240</v>
       </c>
       <c r="C241">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D241" t="s">
         <v>6</v>
@@ -10236,7 +10362,7 @@
         <v>241</v>
       </c>
       <c r="C242">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D242" t="s">
         <v>6</v>
@@ -10269,7 +10395,7 @@
         <v>242</v>
       </c>
       <c r="C243">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D243" t="s">
         <v>8</v>
@@ -10302,7 +10428,7 @@
         <v>243</v>
       </c>
       <c r="C244">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D244" t="s">
         <v>6</v>
@@ -10335,7 +10461,7 @@
         <v>244</v>
       </c>
       <c r="C245">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D245" t="s">
         <v>6</v>
@@ -10368,7 +10494,7 @@
         <v>245</v>
       </c>
       <c r="C246">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D246" t="s">
         <v>6</v>
@@ -10401,7 +10527,7 @@
         <v>246</v>
       </c>
       <c r="C247">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D247" t="s">
         <v>6</v>
@@ -10434,7 +10560,7 @@
         <v>247</v>
       </c>
       <c r="C248">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D248" t="s">
         <v>6</v>
@@ -10467,7 +10593,7 @@
         <v>248</v>
       </c>
       <c r="C249">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D249" t="s">
         <v>8</v>
@@ -10500,7 +10626,7 @@
         <v>249</v>
       </c>
       <c r="C250">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D250" t="s">
         <v>8</v>
@@ -10533,7 +10659,7 @@
         <v>250</v>
       </c>
       <c r="C251">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D251" t="s">
         <v>8</v>
@@ -10566,7 +10692,7 @@
         <v>251</v>
       </c>
       <c r="C252">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D252" t="s">
         <v>6</v>
@@ -10629,7 +10755,7 @@
         <v>253</v>
       </c>
       <c r="C254">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D254" t="s">
         <v>6</v>
@@ -10669,7 +10795,7 @@
         <v>254</v>
       </c>
       <c r="C255">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D255" t="s">
         <v>6</v>
@@ -10709,7 +10835,7 @@
         <v>255</v>
       </c>
       <c r="C256">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D256" t="s">
         <v>6</v>
@@ -10749,7 +10875,7 @@
         <v>256</v>
       </c>
       <c r="C257">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D257" t="s">
         <v>6</v>
@@ -10789,7 +10915,7 @@
         <v>257</v>
       </c>
       <c r="C258">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D258" t="s">
         <v>6</v>
@@ -10829,7 +10955,7 @@
         <v>258</v>
       </c>
       <c r="C259">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D259" t="s">
         <v>6</v>
@@ -10859,7 +10985,7 @@
         <v>259</v>
       </c>
       <c r="C260">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D260" t="s">
         <v>6</v>
@@ -10889,7 +11015,7 @@
         <v>260</v>
       </c>
       <c r="C261">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D261" t="s">
         <v>6</v>
@@ -10919,7 +11045,7 @@
         <v>261</v>
       </c>
       <c r="C262">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D262" t="s">
         <v>6</v>
@@ -10949,7 +11075,7 @@
         <v>262</v>
       </c>
       <c r="C263">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D263" t="s">
         <v>6</v>
@@ -10979,7 +11105,7 @@
         <v>263</v>
       </c>
       <c r="C264">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D264" t="s">
         <v>6</v>
@@ -11009,7 +11135,7 @@
         <v>264</v>
       </c>
       <c r="C265">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D265" t="s">
         <v>6</v>
@@ -11039,7 +11165,7 @@
         <v>265</v>
       </c>
       <c r="C266">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D266" t="s">
         <v>6</v>
@@ -11069,7 +11195,7 @@
         <v>266</v>
       </c>
       <c r="C267">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D267" t="s">
         <v>6</v>
@@ -11099,7 +11225,7 @@
         <v>267</v>
       </c>
       <c r="C268">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D268" t="s">
         <v>6</v>
@@ -11132,7 +11258,7 @@
         <v>268</v>
       </c>
       <c r="C269">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D269" t="s">
         <v>6</v>
@@ -11162,7 +11288,7 @@
         <v>269</v>
       </c>
       <c r="C270">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D270" t="s">
         <v>6</v>
@@ -11192,7 +11318,7 @@
         <v>270</v>
       </c>
       <c r="C271">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D271" t="s">
         <v>6</v>
@@ -11222,7 +11348,7 @@
         <v>271</v>
       </c>
       <c r="C272">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D272" t="s">
         <v>6</v>
@@ -11252,7 +11378,7 @@
         <v>272</v>
       </c>
       <c r="C273">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D273" t="s">
         <v>6</v>
@@ -11285,7 +11411,7 @@
         <v>273</v>
       </c>
       <c r="C274">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D274" t="s">
         <v>6</v>
@@ -11315,7 +11441,7 @@
         <v>274</v>
       </c>
       <c r="C275">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D275" t="s">
         <v>6</v>
@@ -11345,7 +11471,7 @@
         <v>275</v>
       </c>
       <c r="C276">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D276" t="s">
         <v>6</v>
@@ -11375,7 +11501,7 @@
         <v>276</v>
       </c>
       <c r="C277">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D277" t="s">
         <v>6</v>
@@ -11405,7 +11531,7 @@
         <v>277</v>
       </c>
       <c r="C278">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D278" t="s">
         <v>6</v>
@@ -11435,7 +11561,7 @@
         <v>278</v>
       </c>
       <c r="C279">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D279" t="s">
         <v>6</v>
@@ -11465,7 +11591,7 @@
         <v>279</v>
       </c>
       <c r="C280">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D280" t="s">
         <v>6</v>
@@ -11495,7 +11621,7 @@
         <v>280</v>
       </c>
       <c r="C281">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D281" t="s">
         <v>6</v>
@@ -11525,7 +11651,7 @@
         <v>281</v>
       </c>
       <c r="C282">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D282" t="s">
         <v>6</v>
@@ -11555,7 +11681,7 @@
         <v>282</v>
       </c>
       <c r="C283">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D283" t="s">
         <v>6</v>
@@ -11585,7 +11711,7 @@
         <v>283</v>
       </c>
       <c r="C284">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D284" t="s">
         <v>6</v>
@@ -11615,7 +11741,7 @@
         <v>284</v>
       </c>
       <c r="C285">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D285" t="s">
         <v>6</v>
@@ -11645,7 +11771,7 @@
         <v>285</v>
       </c>
       <c r="C286">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D286" t="s">
         <v>6</v>
@@ -11675,7 +11801,7 @@
         <v>286</v>
       </c>
       <c r="C287">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D287" t="s">
         <v>6</v>
@@ -11705,7 +11831,7 @@
         <v>287</v>
       </c>
       <c r="C288">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D288" t="s">
         <v>6</v>
@@ -11735,7 +11861,7 @@
         <v>288</v>
       </c>
       <c r="C289">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D289" t="s">
         <v>6</v>
@@ -11765,7 +11891,7 @@
         <v>289</v>
       </c>
       <c r="C290">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D290" t="s">
         <v>6</v>
@@ -11795,7 +11921,7 @@
         <v>290</v>
       </c>
       <c r="C291">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D291" t="s">
         <v>6</v>
@@ -11825,7 +11951,7 @@
         <v>291</v>
       </c>
       <c r="C292">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D292" t="s">
         <v>6</v>
@@ -11855,7 +11981,7 @@
         <v>292</v>
       </c>
       <c r="C293">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D293" t="s">
         <v>6</v>
@@ -11885,7 +12011,7 @@
         <v>293</v>
       </c>
       <c r="C294">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D294" t="s">
         <v>6</v>
@@ -11915,7 +12041,7 @@
         <v>294</v>
       </c>
       <c r="C295">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D295" t="s">
         <v>6</v>
@@ -11945,7 +12071,7 @@
         <v>295</v>
       </c>
       <c r="C296">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D296" t="s">
         <v>6</v>
@@ -11975,7 +12101,7 @@
         <v>296</v>
       </c>
       <c r="C297">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D297" t="s">
         <v>6</v>
@@ -12005,7 +12131,7 @@
         <v>297</v>
       </c>
       <c r="C298">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D298" t="s">
         <v>6</v>
@@ -12035,7 +12161,7 @@
         <v>298</v>
       </c>
       <c r="C299">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D299" t="s">
         <v>6</v>
@@ -12050,7 +12176,7 @@
         <v>6</v>
       </c>
       <c r="I299" t="str">
-        <f t="shared" ref="I299:I338" si="9">"/cards/image"&amp;ROW()-1&amp;".jpg"</f>
+        <f t="shared" ref="I299:I361" si="9">"/cards/image"&amp;ROW()-1&amp;".jpg"</f>
         <v>/cards/image298.jpg</v>
       </c>
       <c r="M299" t="s">
@@ -12065,7 +12191,7 @@
         <v>299</v>
       </c>
       <c r="C300">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D300" t="s">
         <v>6</v>
@@ -12095,7 +12221,7 @@
         <v>300</v>
       </c>
       <c r="C301">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D301" t="s">
         <v>6</v>
@@ -12125,7 +12251,7 @@
         <v>301</v>
       </c>
       <c r="C302">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D302" t="s">
         <v>6</v>
@@ -12155,7 +12281,7 @@
         <v>302</v>
       </c>
       <c r="C303">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D303" t="s">
         <v>6</v>
@@ -12185,7 +12311,7 @@
         <v>303</v>
       </c>
       <c r="C304">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D304" t="s">
         <v>6</v>
@@ -12215,7 +12341,7 @@
         <v>304</v>
       </c>
       <c r="C305">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D305" t="s">
         <v>6</v>
@@ -12245,7 +12371,7 @@
         <v>305</v>
       </c>
       <c r="C306">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D306" t="s">
         <v>6</v>
@@ -12275,7 +12401,7 @@
         <v>306</v>
       </c>
       <c r="C307">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D307" t="s">
         <v>6</v>
@@ -12305,7 +12431,7 @@
         <v>307</v>
       </c>
       <c r="C308">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D308" t="s">
         <v>6</v>
@@ -12335,7 +12461,7 @@
         <v>308</v>
       </c>
       <c r="C309">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D309" t="s">
         <v>6</v>
@@ -12365,7 +12491,7 @@
         <v>309</v>
       </c>
       <c r="C310">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D310" t="s">
         <v>6</v>
@@ -12395,7 +12521,7 @@
         <v>310</v>
       </c>
       <c r="C311">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D311" t="s">
         <v>6</v>
@@ -12425,7 +12551,7 @@
         <v>311</v>
       </c>
       <c r="C312">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D312" t="s">
         <v>6</v>
@@ -12455,7 +12581,7 @@
         <v>312</v>
       </c>
       <c r="C313">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D313" t="s">
         <v>6</v>
@@ -12485,7 +12611,7 @@
         <v>313</v>
       </c>
       <c r="C314">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D314" t="s">
         <v>6</v>
@@ -12515,7 +12641,7 @@
         <v>314</v>
       </c>
       <c r="C315">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D315" t="s">
         <v>8</v>
@@ -12545,7 +12671,7 @@
         <v>315</v>
       </c>
       <c r="C316">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D316" t="s">
         <v>6</v>
@@ -12575,7 +12701,7 @@
         <v>316</v>
       </c>
       <c r="C317">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D317" t="s">
         <v>6</v>
@@ -12605,7 +12731,7 @@
         <v>317</v>
       </c>
       <c r="C318">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D318" t="s">
         <v>6</v>
@@ -12635,7 +12761,7 @@
         <v>318</v>
       </c>
       <c r="C319">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D319" t="s">
         <v>6</v>
@@ -12665,7 +12791,7 @@
         <v>319</v>
       </c>
       <c r="C320">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D320" t="s">
         <v>6</v>
@@ -12695,7 +12821,7 @@
         <v>320</v>
       </c>
       <c r="C321">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D321" t="s">
         <v>6</v>
@@ -12725,7 +12851,7 @@
         <v>321</v>
       </c>
       <c r="C322">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D322" t="s">
         <v>6</v>
@@ -12755,7 +12881,7 @@
         <v>322</v>
       </c>
       <c r="C323">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D323" t="s">
         <v>6</v>
@@ -12785,7 +12911,7 @@
         <v>323</v>
       </c>
       <c r="C324">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D324" t="s">
         <v>6</v>
@@ -12815,7 +12941,7 @@
         <v>324</v>
       </c>
       <c r="C325">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D325" t="s">
         <v>6</v>
@@ -12845,7 +12971,7 @@
         <v>325</v>
       </c>
       <c r="C326">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D326" t="s">
         <v>6</v>
@@ -12878,7 +13004,7 @@
         <v>326</v>
       </c>
       <c r="C327">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D327" t="s">
         <v>6</v>
@@ -12908,7 +13034,7 @@
         <v>327</v>
       </c>
       <c r="C328">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D328" t="s">
         <v>6</v>
@@ -12938,7 +13064,7 @@
         <v>328</v>
       </c>
       <c r="C329">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D329" t="s">
         <v>6</v>
@@ -12968,7 +13094,7 @@
         <v>329</v>
       </c>
       <c r="C330">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D330" t="s">
         <v>6</v>
@@ -13001,7 +13127,7 @@
         <v>330</v>
       </c>
       <c r="C331">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D331" t="s">
         <v>6</v>
@@ -13034,7 +13160,7 @@
         <v>331</v>
       </c>
       <c r="C332">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D332" t="s">
         <v>6</v>
@@ -13067,7 +13193,7 @@
         <v>332</v>
       </c>
       <c r="C333">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D333" t="s">
         <v>6</v>
@@ -13100,7 +13226,7 @@
         <v>333</v>
       </c>
       <c r="C334">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D334" t="s">
         <v>6</v>
@@ -13130,7 +13256,7 @@
         <v>334</v>
       </c>
       <c r="C335">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D335" t="s">
         <v>6</v>
@@ -13160,7 +13286,7 @@
         <v>335</v>
       </c>
       <c r="C336">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D336" t="s">
         <v>6</v>
@@ -13185,7 +13311,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>624</v>
       </c>
@@ -13193,7 +13319,7 @@
         <v>336</v>
       </c>
       <c r="C337">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D337" t="s">
         <v>6</v>
@@ -13218,7 +13344,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>625</v>
       </c>
@@ -13226,7 +13352,7 @@
         <v>337</v>
       </c>
       <c r="C338">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D338" t="s">
         <v>6</v>
@@ -13248,6 +13374,788 @@
         <v>11</v>
       </c>
       <c r="M338" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>707</v>
+      </c>
+      <c r="B339">
+        <v>338</v>
+      </c>
+      <c r="C339">
+        <v>1</v>
+      </c>
+      <c r="D339" t="s">
+        <v>8</v>
+      </c>
+      <c r="E339" t="s">
+        <v>730</v>
+      </c>
+      <c r="F339" t="s">
+        <v>52</v>
+      </c>
+      <c r="G339">
+        <v>98</v>
+      </c>
+      <c r="I339" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image338.jpg</v>
+      </c>
+      <c r="J339" t="str">
+        <f t="shared" ref="J339:J361" si="10">"/cards/alt-image"&amp;ROW(A338)&amp;".jpg"</f>
+        <v>/cards/alt-image338.jpg</v>
+      </c>
+      <c r="M339" t="s">
+        <v>82</v>
+      </c>
+      <c r="N339" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>708</v>
+      </c>
+      <c r="B340">
+        <v>339</v>
+      </c>
+      <c r="C340">
+        <v>1</v>
+      </c>
+      <c r="D340" t="s">
+        <v>8</v>
+      </c>
+      <c r="E340" t="s">
+        <v>728</v>
+      </c>
+      <c r="F340" t="s">
+        <v>52</v>
+      </c>
+      <c r="G340">
+        <v>179</v>
+      </c>
+      <c r="I340" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image339.jpg</v>
+      </c>
+      <c r="J340" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image339.jpg</v>
+      </c>
+      <c r="M340" t="s">
+        <v>82</v>
+      </c>
+      <c r="N340" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>709</v>
+      </c>
+      <c r="B341">
+        <v>340</v>
+      </c>
+      <c r="C341">
+        <v>1</v>
+      </c>
+      <c r="D341" t="s">
+        <v>8</v>
+      </c>
+      <c r="E341" t="s">
+        <v>729</v>
+      </c>
+      <c r="F341" t="s">
+        <v>52</v>
+      </c>
+      <c r="G341">
+        <v>289</v>
+      </c>
+      <c r="I341" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image340.jpg</v>
+      </c>
+      <c r="J341" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image340.jpg</v>
+      </c>
+      <c r="M341" t="s">
+        <v>82</v>
+      </c>
+      <c r="N341" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="342" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>710</v>
+      </c>
+      <c r="B342">
+        <v>341</v>
+      </c>
+      <c r="C342">
+        <v>1</v>
+      </c>
+      <c r="D342" t="s">
+        <v>8</v>
+      </c>
+      <c r="E342" t="s">
+        <v>731</v>
+      </c>
+      <c r="F342" t="s">
+        <v>52</v>
+      </c>
+      <c r="G342">
+        <v>280</v>
+      </c>
+      <c r="I342" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image341.jpg</v>
+      </c>
+      <c r="J342" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image341.jpg</v>
+      </c>
+      <c r="M342" t="s">
+        <v>82</v>
+      </c>
+      <c r="N342" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>711</v>
+      </c>
+      <c r="B343">
+        <v>342</v>
+      </c>
+      <c r="C343">
+        <v>1</v>
+      </c>
+      <c r="D343" t="s">
+        <v>8</v>
+      </c>
+      <c r="E343" t="s">
+        <v>732</v>
+      </c>
+      <c r="F343" t="s">
+        <v>52</v>
+      </c>
+      <c r="G343">
+        <v>69</v>
+      </c>
+      <c r="I343" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image342.jpg</v>
+      </c>
+      <c r="J343" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image342.jpg</v>
+      </c>
+      <c r="M343" t="s">
+        <v>82</v>
+      </c>
+      <c r="N343" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="344" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>712</v>
+      </c>
+      <c r="B344">
+        <v>343</v>
+      </c>
+      <c r="C344">
+        <v>1</v>
+      </c>
+      <c r="D344" t="s">
+        <v>8</v>
+      </c>
+      <c r="E344" t="s">
+        <v>733</v>
+      </c>
+      <c r="F344" t="s">
+        <v>52</v>
+      </c>
+      <c r="G344">
+        <v>89</v>
+      </c>
+      <c r="I344" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image343.jpg</v>
+      </c>
+      <c r="J344" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image343.jpg</v>
+      </c>
+      <c r="M344" t="s">
+        <v>82</v>
+      </c>
+      <c r="N344" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>713</v>
+      </c>
+      <c r="B345">
+        <v>344</v>
+      </c>
+      <c r="C345">
+        <v>1</v>
+      </c>
+      <c r="D345" t="s">
+        <v>6</v>
+      </c>
+      <c r="E345" t="s">
+        <v>735</v>
+      </c>
+      <c r="F345" t="s">
+        <v>33</v>
+      </c>
+      <c r="G345">
+        <v>289</v>
+      </c>
+      <c r="I345" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image344.jpg</v>
+      </c>
+      <c r="J345" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image344.jpg</v>
+      </c>
+      <c r="M345" t="s">
+        <v>82</v>
+      </c>
+      <c r="N345" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>714</v>
+      </c>
+      <c r="B346">
+        <v>345</v>
+      </c>
+      <c r="C346">
+        <v>1</v>
+      </c>
+      <c r="D346" t="s">
+        <v>8</v>
+      </c>
+      <c r="E346" t="s">
+        <v>734</v>
+      </c>
+      <c r="F346" t="s">
+        <v>43</v>
+      </c>
+      <c r="G346">
+        <v>98</v>
+      </c>
+      <c r="I346" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image345.jpg</v>
+      </c>
+      <c r="J346" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image345.jpg</v>
+      </c>
+      <c r="M346" t="s">
+        <v>82</v>
+      </c>
+      <c r="N346" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>715</v>
+      </c>
+      <c r="B347">
+        <v>346</v>
+      </c>
+      <c r="C347">
+        <v>1</v>
+      </c>
+      <c r="D347" t="s">
+        <v>8</v>
+      </c>
+      <c r="E347" t="s">
+        <v>736</v>
+      </c>
+      <c r="F347" t="s">
+        <v>52</v>
+      </c>
+      <c r="G347">
+        <v>110</v>
+      </c>
+      <c r="I347" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image346.jpg</v>
+      </c>
+      <c r="J347" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image346.jpg</v>
+      </c>
+      <c r="M347" t="s">
+        <v>82</v>
+      </c>
+      <c r="N347" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="348" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>716</v>
+      </c>
+      <c r="B348">
+        <v>347</v>
+      </c>
+      <c r="C348">
+        <v>1</v>
+      </c>
+      <c r="D348" t="s">
+        <v>8</v>
+      </c>
+      <c r="E348" t="s">
+        <v>737</v>
+      </c>
+      <c r="F348" t="s">
+        <v>128</v>
+      </c>
+      <c r="G348">
+        <v>119</v>
+      </c>
+      <c r="I348" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image347.jpg</v>
+      </c>
+      <c r="J348" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image347.jpg</v>
+      </c>
+      <c r="M348" t="s">
+        <v>82</v>
+      </c>
+      <c r="N348" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>717</v>
+      </c>
+      <c r="B349">
+        <v>348</v>
+      </c>
+      <c r="C349">
+        <v>1</v>
+      </c>
+      <c r="D349" t="s">
+        <v>8</v>
+      </c>
+      <c r="E349" t="s">
+        <v>738</v>
+      </c>
+      <c r="F349" t="s">
+        <v>43</v>
+      </c>
+      <c r="G349">
+        <v>980</v>
+      </c>
+      <c r="I349" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image348.jpg</v>
+      </c>
+      <c r="J349" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image348.jpg</v>
+      </c>
+      <c r="M349" t="s">
+        <v>82</v>
+      </c>
+      <c r="N349" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="350" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>718</v>
+      </c>
+      <c r="B350">
+        <v>349</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+      <c r="D350" t="s">
+        <v>8</v>
+      </c>
+      <c r="E350" t="s">
+        <v>739</v>
+      </c>
+      <c r="F350" t="s">
+        <v>107</v>
+      </c>
+      <c r="G350">
+        <v>129</v>
+      </c>
+      <c r="I350" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image349.jpg</v>
+      </c>
+      <c r="J350" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image349.jpg</v>
+      </c>
+      <c r="M350" t="s">
+        <v>82</v>
+      </c>
+      <c r="N350" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="351" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>719</v>
+      </c>
+      <c r="B351">
+        <v>350</v>
+      </c>
+      <c r="C351">
+        <v>1</v>
+      </c>
+      <c r="D351" t="s">
+        <v>8</v>
+      </c>
+      <c r="E351" t="s">
+        <v>740</v>
+      </c>
+      <c r="F351" t="s">
+        <v>107</v>
+      </c>
+      <c r="G351">
+        <v>89</v>
+      </c>
+      <c r="I351" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image350.jpg</v>
+      </c>
+      <c r="J351" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image350.jpg</v>
+      </c>
+      <c r="M351" t="s">
+        <v>82</v>
+      </c>
+      <c r="N351" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="352" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>720</v>
+      </c>
+      <c r="B352">
+        <v>351</v>
+      </c>
+      <c r="C352">
+        <v>1</v>
+      </c>
+      <c r="D352" t="s">
+        <v>8</v>
+      </c>
+      <c r="E352" t="s">
+        <v>741</v>
+      </c>
+      <c r="F352" t="s">
+        <v>43</v>
+      </c>
+      <c r="G352">
+        <v>459</v>
+      </c>
+      <c r="I352" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image351.jpg</v>
+      </c>
+      <c r="J352" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image351.jpg</v>
+      </c>
+      <c r="M352" t="s">
+        <v>82</v>
+      </c>
+      <c r="N352" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="353" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>721</v>
+      </c>
+      <c r="B353">
+        <v>352</v>
+      </c>
+      <c r="C353">
+        <v>1</v>
+      </c>
+      <c r="D353" t="s">
+        <v>6</v>
+      </c>
+      <c r="E353" t="s">
+        <v>742</v>
+      </c>
+      <c r="F353" t="s">
+        <v>662</v>
+      </c>
+      <c r="G353">
+        <v>980</v>
+      </c>
+      <c r="I353" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image352.jpg</v>
+      </c>
+      <c r="J353" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image352.jpg</v>
+      </c>
+      <c r="M353" t="s">
+        <v>82</v>
+      </c>
+      <c r="N353" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="354" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>722</v>
+      </c>
+      <c r="B354">
+        <v>353</v>
+      </c>
+      <c r="C354">
+        <v>1</v>
+      </c>
+      <c r="D354" t="s">
+        <v>6</v>
+      </c>
+      <c r="E354" t="s">
+        <v>743</v>
+      </c>
+      <c r="F354" t="s">
+        <v>31</v>
+      </c>
+      <c r="G354">
+        <v>329</v>
+      </c>
+      <c r="I354" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image353.jpg</v>
+      </c>
+      <c r="J354" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image353.jpg</v>
+      </c>
+      <c r="M354" t="s">
+        <v>82</v>
+      </c>
+      <c r="N354" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="355" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>723</v>
+      </c>
+      <c r="B355">
+        <v>354</v>
+      </c>
+      <c r="C355">
+        <v>1</v>
+      </c>
+      <c r="D355" t="s">
+        <v>6</v>
+      </c>
+      <c r="E355" t="s">
+        <v>744</v>
+      </c>
+      <c r="F355" t="s">
+        <v>662</v>
+      </c>
+      <c r="G355">
+        <v>125</v>
+      </c>
+      <c r="H355" t="s">
+        <v>11</v>
+      </c>
+      <c r="I355" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image354.jpg</v>
+      </c>
+      <c r="J355" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image354.jpg</v>
+      </c>
+      <c r="M355" t="s">
+        <v>82</v>
+      </c>
+      <c r="N355" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>724</v>
+      </c>
+      <c r="B356">
+        <v>355</v>
+      </c>
+      <c r="C356">
+        <v>1</v>
+      </c>
+      <c r="D356" t="s">
+        <v>6</v>
+      </c>
+      <c r="E356" t="s">
+        <v>745</v>
+      </c>
+      <c r="F356" t="s">
+        <v>469</v>
+      </c>
+      <c r="G356">
+        <v>129</v>
+      </c>
+      <c r="H356" t="s">
+        <v>11</v>
+      </c>
+      <c r="I356" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image355.jpg</v>
+      </c>
+      <c r="J356" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image355.jpg</v>
+      </c>
+      <c r="M356" t="s">
+        <v>82</v>
+      </c>
+      <c r="N356" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="357" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>725</v>
+      </c>
+      <c r="B357">
+        <v>356</v>
+      </c>
+      <c r="C357">
+        <v>1</v>
+      </c>
+      <c r="D357" t="s">
+        <v>6</v>
+      </c>
+      <c r="E357" t="s">
+        <v>746</v>
+      </c>
+      <c r="F357" t="s">
+        <v>469</v>
+      </c>
+      <c r="G357">
+        <v>298</v>
+      </c>
+      <c r="H357" t="s">
+        <v>11</v>
+      </c>
+      <c r="I357" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image356.jpg</v>
+      </c>
+      <c r="J357" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image356.jpg</v>
+      </c>
+      <c r="M357" t="s">
+        <v>82</v>
+      </c>
+      <c r="N357" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="358" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>726</v>
+      </c>
+      <c r="B358">
+        <v>357</v>
+      </c>
+      <c r="C358">
+        <v>1</v>
+      </c>
+      <c r="D358" t="s">
+        <v>6</v>
+      </c>
+      <c r="E358" t="s">
+        <v>747</v>
+      </c>
+      <c r="F358" t="s">
+        <v>469</v>
+      </c>
+      <c r="G358">
+        <v>849</v>
+      </c>
+      <c r="I358" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image357.jpg</v>
+      </c>
+      <c r="J358" t="str">
+        <f t="shared" si="10"/>
+        <v>/cards/alt-image357.jpg</v>
+      </c>
+      <c r="M358" t="s">
+        <v>82</v>
+      </c>
+      <c r="N358" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>727</v>
+      </c>
+      <c r="B359">
+        <v>358</v>
+      </c>
+      <c r="C359">
+        <v>30</v>
+      </c>
+      <c r="D359" t="s">
+        <v>8</v>
+      </c>
+      <c r="E359" t="s">
+        <v>748</v>
+      </c>
+      <c r="F359" t="s">
+        <v>534</v>
+      </c>
+      <c r="G359">
+        <v>2</v>
+      </c>
+      <c r="H359" t="s">
+        <v>11</v>
+      </c>
+      <c r="I359" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image358.jpg</v>
+      </c>
+      <c r="M359" t="s">
         <v>122</v>
       </c>
     </row>

--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Berni\Desktop\coleccion-tarjetas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F9C688-CDB9-4AAD-BB4F-DBA52A1F1AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F82F3A0-D79E-48F4-AFA1-C95561B05E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50880" yWindow="330" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
+    <workbookView xWindow="47325" yWindow="495" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="751">
   <si>
     <t>id</t>
   </si>
@@ -2283,6 +2283,12 @@
   </si>
   <si>
     <t>Pack sealed Panini Sticker Pack Fifa World Cup Russia 2018</t>
+  </si>
+  <si>
+    <t>Card-359</t>
+  </si>
+  <si>
+    <t>Pack sealed 2019-20 Topps Champions league sticker</t>
   </si>
 </sst>
 </file>
@@ -2660,7 +2666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DAA126C-D60B-4EC0-8FDE-28B90D0445C8}">
-  <dimension ref="A1:N359"/>
+  <dimension ref="A1:N360"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="36.140625" customWidth="1"/>
@@ -12176,7 +12182,7 @@
         <v>6</v>
       </c>
       <c r="I299" t="str">
-        <f t="shared" ref="I299:I361" si="9">"/cards/image"&amp;ROW()-1&amp;".jpg"</f>
+        <f t="shared" ref="I299:I360" si="9">"/cards/image"&amp;ROW()-1&amp;".jpg"</f>
         <v>/cards/image298.jpg</v>
       </c>
       <c r="M299" t="s">
@@ -13404,7 +13410,7 @@
         <v>/cards/image338.jpg</v>
       </c>
       <c r="J339" t="str">
-        <f t="shared" ref="J339:J361" si="10">"/cards/alt-image"&amp;ROW(A338)&amp;".jpg"</f>
+        <f t="shared" ref="J339:J358" si="10">"/cards/alt-image"&amp;ROW(A338)&amp;".jpg"</f>
         <v>/cards/alt-image338.jpg</v>
       </c>
       <c r="M339" t="s">
@@ -14156,6 +14162,33 @@
         <v>/cards/image358.jpg</v>
       </c>
       <c r="M359" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>749</v>
+      </c>
+      <c r="B360">
+        <v>359</v>
+      </c>
+      <c r="C360">
+        <v>100</v>
+      </c>
+      <c r="D360" t="s">
+        <v>8</v>
+      </c>
+      <c r="E360" t="s">
+        <v>750</v>
+      </c>
+      <c r="G360">
+        <v>5</v>
+      </c>
+      <c r="I360" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image359.jpg</v>
+      </c>
+      <c r="M360" t="s">
         <v>122</v>
       </c>
     </row>

--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Berni\Desktop\coleccion-tarjetas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F82F3A0-D79E-48F4-AFA1-C95561B05E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C167B6E-0192-4BAC-B1A1-49A6F4E2F532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47325" yWindow="495" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
+    <workbookView xWindow="49980" yWindow="135" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="771">
   <si>
     <t>id</t>
   </si>
@@ -2289,6 +2289,66 @@
   </si>
   <si>
     <t>Pack sealed 2019-20 Topps Champions league sticker</t>
+  </si>
+  <si>
+    <t>Card-360</t>
+  </si>
+  <si>
+    <t>Card-361</t>
+  </si>
+  <si>
+    <t>Card-362</t>
+  </si>
+  <si>
+    <t>Card-363</t>
+  </si>
+  <si>
+    <t>Card-364</t>
+  </si>
+  <si>
+    <t>Card-365</t>
+  </si>
+  <si>
+    <t>Card-366</t>
+  </si>
+  <si>
+    <t>Card-367</t>
+  </si>
+  <si>
+    <t>Card-368</t>
+  </si>
+  <si>
+    <t>2021 Immaculate Collection NFL SHIELD PATCH AUTO 1/1 BGS 8.5</t>
+  </si>
+  <si>
+    <t>nfl</t>
+  </si>
+  <si>
+    <t>2020 National Treasures NFL Gear ROOKIE PATCH AUTO /25 MBA AUTH</t>
+  </si>
+  <si>
+    <t>2020 National Treasures Hidden ROOKIE PATCH AUTO /5 #165 MBA AUTH</t>
+  </si>
+  <si>
+    <t>2020 National Treasures S &amp; S nike swosh ROOKIE PATCH AUTO /3 #165 MBA AUTH</t>
+  </si>
+  <si>
+    <t>2020 Panini Encased Emerald ROOKIE PATCH AUTO /5 #109 BGS 9 MINT</t>
+  </si>
+  <si>
+    <t>2020 National Treasures Holo Silver ROOKIE PATCH AUTO /25 BGS 7.5</t>
+  </si>
+  <si>
+    <t>2021 Panini Flawless Collegiate Star PATCH AUTO /25 MBA AUTH</t>
+  </si>
+  <si>
+    <t>Justin Herbert</t>
+  </si>
+  <si>
+    <t>2021 Panini Flawless Collegiate Emerald PATCH AUTO /5 MBA AUTH</t>
+  </si>
+  <si>
+    <t>2021 Panini Flawless Collegiate Dual Ruby PATCH AUTO /15 MBA AUTH</t>
   </si>
 </sst>
 </file>
@@ -2666,7 +2726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DAA126C-D60B-4EC0-8FDE-28B90D0445C8}">
-  <dimension ref="A1:N360"/>
+  <dimension ref="A1:N369"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="36.140625" customWidth="1"/>
@@ -2843,7 +2903,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -2883,7 +2943,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -3049,7 +3109,7 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
@@ -3212,7 +3272,7 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
@@ -3252,7 +3312,7 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
@@ -12182,7 +12242,7 @@
         <v>6</v>
       </c>
       <c r="I299" t="str">
-        <f t="shared" ref="I299:I360" si="9">"/cards/image"&amp;ROW()-1&amp;".jpg"</f>
+        <f t="shared" ref="I299:I362" si="9">"/cards/image"&amp;ROW()-1&amp;".jpg"</f>
         <v>/cards/image298.jpg</v>
       </c>
       <c r="M299" t="s">
@@ -14181,6 +14241,9 @@
       <c r="E360" t="s">
         <v>750</v>
       </c>
+      <c r="F360" t="s">
+        <v>534</v>
+      </c>
       <c r="G360">
         <v>5</v>
       </c>
@@ -14190,6 +14253,360 @@
       </c>
       <c r="M360" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>751</v>
+      </c>
+      <c r="B361">
+        <v>360</v>
+      </c>
+      <c r="C361">
+        <v>1</v>
+      </c>
+      <c r="D361" t="s">
+        <v>761</v>
+      </c>
+      <c r="E361" t="s">
+        <v>760</v>
+      </c>
+      <c r="F361" t="s">
+        <v>99</v>
+      </c>
+      <c r="G361">
+        <v>750</v>
+      </c>
+      <c r="H361" t="s">
+        <v>11</v>
+      </c>
+      <c r="I361" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image360.jpg</v>
+      </c>
+      <c r="J361" t="str">
+        <f t="shared" ref="J361:J369" si="11">"/cards/alt-image"&amp;ROW(A360)&amp;".jpg"</f>
+        <v>/cards/alt-image360.jpg</v>
+      </c>
+      <c r="M361" t="s">
+        <v>82</v>
+      </c>
+      <c r="N361" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>752</v>
+      </c>
+      <c r="B362">
+        <v>361</v>
+      </c>
+      <c r="C362">
+        <v>1</v>
+      </c>
+      <c r="D362" t="s">
+        <v>761</v>
+      </c>
+      <c r="E362" t="s">
+        <v>762</v>
+      </c>
+      <c r="F362" t="s">
+        <v>99</v>
+      </c>
+      <c r="G362">
+        <v>190</v>
+      </c>
+      <c r="H362" t="s">
+        <v>11</v>
+      </c>
+      <c r="I362" t="str">
+        <f t="shared" si="9"/>
+        <v>/cards/image361.jpg</v>
+      </c>
+      <c r="J362" t="str">
+        <f t="shared" si="11"/>
+        <v>/cards/alt-image361.jpg</v>
+      </c>
+      <c r="M362" t="s">
+        <v>82</v>
+      </c>
+      <c r="N362" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>753</v>
+      </c>
+      <c r="B363">
+        <v>362</v>
+      </c>
+      <c r="C363">
+        <v>1</v>
+      </c>
+      <c r="D363" t="s">
+        <v>761</v>
+      </c>
+      <c r="E363" t="s">
+        <v>763</v>
+      </c>
+      <c r="F363" t="s">
+        <v>99</v>
+      </c>
+      <c r="G363">
+        <v>480</v>
+      </c>
+      <c r="I363" t="str">
+        <f t="shared" ref="I363:I369" si="12">"/cards/image"&amp;ROW()-1&amp;".jpg"</f>
+        <v>/cards/image362.jpg</v>
+      </c>
+      <c r="J363" t="str">
+        <f t="shared" si="11"/>
+        <v>/cards/alt-image362.jpg</v>
+      </c>
+      <c r="M363" t="s">
+        <v>82</v>
+      </c>
+      <c r="N363" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>754</v>
+      </c>
+      <c r="B364">
+        <v>363</v>
+      </c>
+      <c r="C364">
+        <v>1</v>
+      </c>
+      <c r="D364" t="s">
+        <v>761</v>
+      </c>
+      <c r="E364" t="s">
+        <v>764</v>
+      </c>
+      <c r="F364" t="s">
+        <v>99</v>
+      </c>
+      <c r="G364">
+        <v>620</v>
+      </c>
+      <c r="I364" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image363.jpg</v>
+      </c>
+      <c r="J364" t="str">
+        <f t="shared" si="11"/>
+        <v>/cards/alt-image363.jpg</v>
+      </c>
+      <c r="M364" t="s">
+        <v>82</v>
+      </c>
+      <c r="N364" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>755</v>
+      </c>
+      <c r="B365">
+        <v>364</v>
+      </c>
+      <c r="C365">
+        <v>1</v>
+      </c>
+      <c r="D365" t="s">
+        <v>761</v>
+      </c>
+      <c r="E365" t="s">
+        <v>765</v>
+      </c>
+      <c r="F365" t="s">
+        <v>99</v>
+      </c>
+      <c r="G365">
+        <v>165</v>
+      </c>
+      <c r="H365" t="s">
+        <v>11</v>
+      </c>
+      <c r="I365" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image364.jpg</v>
+      </c>
+      <c r="J365" t="str">
+        <f t="shared" si="11"/>
+        <v>/cards/alt-image364.jpg</v>
+      </c>
+      <c r="M365" t="s">
+        <v>82</v>
+      </c>
+      <c r="N365" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>756</v>
+      </c>
+      <c r="B366">
+        <v>365</v>
+      </c>
+      <c r="C366">
+        <v>1</v>
+      </c>
+      <c r="D366" t="s">
+        <v>761</v>
+      </c>
+      <c r="E366" t="s">
+        <v>766</v>
+      </c>
+      <c r="F366" t="s">
+        <v>99</v>
+      </c>
+      <c r="G366">
+        <v>259</v>
+      </c>
+      <c r="H366" t="s">
+        <v>11</v>
+      </c>
+      <c r="I366" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image365.jpg</v>
+      </c>
+      <c r="J366" t="str">
+        <f t="shared" si="11"/>
+        <v>/cards/alt-image365.jpg</v>
+      </c>
+      <c r="M366" t="s">
+        <v>82</v>
+      </c>
+      <c r="N366" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>757</v>
+      </c>
+      <c r="B367">
+        <v>366</v>
+      </c>
+      <c r="C367">
+        <v>1</v>
+      </c>
+      <c r="D367" t="s">
+        <v>761</v>
+      </c>
+      <c r="E367" t="s">
+        <v>767</v>
+      </c>
+      <c r="F367" t="s">
+        <v>768</v>
+      </c>
+      <c r="G367">
+        <v>590</v>
+      </c>
+      <c r="H367" t="s">
+        <v>11</v>
+      </c>
+      <c r="I367" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image366.jpg</v>
+      </c>
+      <c r="J367" t="str">
+        <f t="shared" si="11"/>
+        <v>/cards/alt-image366.jpg</v>
+      </c>
+      <c r="M367" t="s">
+        <v>82</v>
+      </c>
+      <c r="N367" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>758</v>
+      </c>
+      <c r="B368">
+        <v>367</v>
+      </c>
+      <c r="C368">
+        <v>1</v>
+      </c>
+      <c r="D368" t="s">
+        <v>761</v>
+      </c>
+      <c r="E368" t="s">
+        <v>769</v>
+      </c>
+      <c r="F368" t="s">
+        <v>768</v>
+      </c>
+      <c r="G368">
+        <v>720</v>
+      </c>
+      <c r="H368" t="s">
+        <v>11</v>
+      </c>
+      <c r="I368" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image367.jpg</v>
+      </c>
+      <c r="J368" t="str">
+        <f t="shared" si="11"/>
+        <v>/cards/alt-image367.jpg</v>
+      </c>
+      <c r="M368" t="s">
+        <v>82</v>
+      </c>
+      <c r="N368" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>759</v>
+      </c>
+      <c r="B369">
+        <v>368</v>
+      </c>
+      <c r="C369">
+        <v>1</v>
+      </c>
+      <c r="D369" t="s">
+        <v>761</v>
+      </c>
+      <c r="E369" t="s">
+        <v>770</v>
+      </c>
+      <c r="F369" t="s">
+        <v>768</v>
+      </c>
+      <c r="G369">
+        <v>640</v>
+      </c>
+      <c r="H369" t="s">
+        <v>11</v>
+      </c>
+      <c r="I369" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image368.jpg</v>
+      </c>
+      <c r="J369" t="str">
+        <f t="shared" si="11"/>
+        <v>/cards/alt-image368.jpg</v>
+      </c>
+      <c r="M369" t="s">
+        <v>82</v>
+      </c>
+      <c r="N369" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Berni\Desktop\coleccion-tarjetas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C167B6E-0192-4BAC-B1A1-49A6F4E2F532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8208B2-0D90-4790-A547-649BA2B445C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="49980" yWindow="135" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
+    <workbookView xWindow="49845" yWindow="135" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="794">
   <si>
     <t>id</t>
   </si>
@@ -2349,6 +2349,75 @@
   </si>
   <si>
     <t>2021 Panini Flawless Collegiate Dual Ruby PATCH AUTO /15 MBA AUTH</t>
+  </si>
+  <si>
+    <t>Card-369</t>
+  </si>
+  <si>
+    <t>Card-370</t>
+  </si>
+  <si>
+    <t>Card-371</t>
+  </si>
+  <si>
+    <t>Card-372</t>
+  </si>
+  <si>
+    <t>2004 Sp Game Used All-Star Sigs Gold  AUTO /14 #MJ BGS 8.5 NM-MT+</t>
+  </si>
+  <si>
+    <t>2006 SPx Winning Combos Michael Jordan &amp; LeBron James PATCH #WC-JJ BGS 9 MINT</t>
+  </si>
+  <si>
+    <t>2007 Ultimate Collection Matchups Michael Jordan &amp; LeBron James PATCH /99 BGS 9</t>
+  </si>
+  <si>
+    <t>2009 Upper Deck First Edition Gold ROOKIE #196 PSA 9 MINT</t>
+  </si>
+  <si>
+    <t>2022 FansMall Light Argentina Purple  RC PATCH AUTO /25 MBA AUTH</t>
+  </si>
+  <si>
+    <t>Card-373</t>
+  </si>
+  <si>
+    <t>Card-374</t>
+  </si>
+  <si>
+    <t>Card-375</t>
+  </si>
+  <si>
+    <t>Card-376</t>
+  </si>
+  <si>
+    <t>Card-377</t>
+  </si>
+  <si>
+    <t>2022 FansMall Light Purple  ROOKIE PATCH AUTO /36 MBA AUTH</t>
+  </si>
+  <si>
+    <t>2021 Panini Flawless Collegiate  PATCH AUTO /25 #PA-JH MBA AUTH</t>
+  </si>
+  <si>
+    <t>Card-378</t>
+  </si>
+  <si>
+    <t>Card-379</t>
+  </si>
+  <si>
+    <t>Card-380</t>
+  </si>
+  <si>
+    <t>2020 National Treasures Stars &amp; Stripes RC PATCH AUTO /20 PSA 8</t>
+  </si>
+  <si>
+    <t>2005 Reflections Signatures Red  AUTO /25 #MJ BGS 9 MINT</t>
+  </si>
+  <si>
+    <t>1997 Skybox Premium Playe  #3 PSA 9 MINT</t>
+  </si>
+  <si>
+    <t>1994 Upper Deck Argentina Premier Division #165 BGS 9 MINT</t>
   </si>
 </sst>
 </file>
@@ -2726,7 +2795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DAA126C-D60B-4EC0-8FDE-28B90D0445C8}">
-  <dimension ref="A1:N369"/>
+  <dimension ref="A1:N381"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="36.140625" customWidth="1"/>
@@ -14358,7 +14427,7 @@
         <v>480</v>
       </c>
       <c r="I363" t="str">
-        <f t="shared" ref="I363:I369" si="12">"/cards/image"&amp;ROW()-1&amp;".jpg"</f>
+        <f t="shared" ref="I363:I381" si="12">"/cards/image"&amp;ROW()-1&amp;".jpg"</f>
         <v>/cards/image362.jpg</v>
       </c>
       <c r="J363" t="str">
@@ -14606,6 +14675,429 @@
         <v>82</v>
       </c>
       <c r="N369" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>771</v>
+      </c>
+      <c r="B370">
+        <v>369</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370" t="s">
+        <v>6</v>
+      </c>
+      <c r="E370" t="s">
+        <v>775</v>
+      </c>
+      <c r="F370" t="s">
+        <v>31</v>
+      </c>
+      <c r="G370">
+        <v>11800</v>
+      </c>
+      <c r="I370" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image369.jpg</v>
+      </c>
+      <c r="M370" t="s">
+        <v>82</v>
+      </c>
+      <c r="N370" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>772</v>
+      </c>
+      <c r="B371">
+        <v>370</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371" t="s">
+        <v>6</v>
+      </c>
+      <c r="E371" t="s">
+        <v>776</v>
+      </c>
+      <c r="F371" t="s">
+        <v>31</v>
+      </c>
+      <c r="G371">
+        <v>1700</v>
+      </c>
+      <c r="H371" t="s">
+        <v>11</v>
+      </c>
+      <c r="I371" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image370.jpg</v>
+      </c>
+      <c r="M371" t="s">
+        <v>82</v>
+      </c>
+      <c r="N371" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>773</v>
+      </c>
+      <c r="B372">
+        <v>371</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372" t="s">
+        <v>6</v>
+      </c>
+      <c r="E372" t="s">
+        <v>777</v>
+      </c>
+      <c r="F372" t="s">
+        <v>31</v>
+      </c>
+      <c r="G372">
+        <v>3000</v>
+      </c>
+      <c r="I372" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image371.jpg</v>
+      </c>
+      <c r="M372" t="s">
+        <v>82</v>
+      </c>
+      <c r="N372" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>774</v>
+      </c>
+      <c r="B373">
+        <v>372</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373" t="s">
+        <v>6</v>
+      </c>
+      <c r="E373" t="s">
+        <v>778</v>
+      </c>
+      <c r="F373" t="s">
+        <v>33</v>
+      </c>
+      <c r="G373">
+        <v>825</v>
+      </c>
+      <c r="I373" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image372.jpg</v>
+      </c>
+      <c r="M373" t="s">
+        <v>82</v>
+      </c>
+      <c r="N373" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>780</v>
+      </c>
+      <c r="B374">
+        <v>373</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374" t="s">
+        <v>8</v>
+      </c>
+      <c r="E374" t="s">
+        <v>779</v>
+      </c>
+      <c r="F374" t="s">
+        <v>107</v>
+      </c>
+      <c r="G374">
+        <v>110</v>
+      </c>
+      <c r="H374" t="s">
+        <v>11</v>
+      </c>
+      <c r="I374" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image373.jpg</v>
+      </c>
+      <c r="M374" t="s">
+        <v>82</v>
+      </c>
+      <c r="N374" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>781</v>
+      </c>
+      <c r="B375">
+        <v>374</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375" t="s">
+        <v>8</v>
+      </c>
+      <c r="E375" t="s">
+        <v>785</v>
+      </c>
+      <c r="F375" t="s">
+        <v>107</v>
+      </c>
+      <c r="G375">
+        <v>130</v>
+      </c>
+      <c r="H375" t="s">
+        <v>11</v>
+      </c>
+      <c r="I375" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image374.jpg</v>
+      </c>
+      <c r="M375" t="s">
+        <v>82</v>
+      </c>
+      <c r="N375" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>782</v>
+      </c>
+      <c r="B376">
+        <v>375</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376" t="s">
+        <v>761</v>
+      </c>
+      <c r="E376" t="s">
+        <v>786</v>
+      </c>
+      <c r="F376" t="s">
+        <v>768</v>
+      </c>
+      <c r="G376">
+        <v>475</v>
+      </c>
+      <c r="H376" t="s">
+        <v>11</v>
+      </c>
+      <c r="I376" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image375.jpg</v>
+      </c>
+      <c r="M376" t="s">
+        <v>82</v>
+      </c>
+      <c r="N376" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>783</v>
+      </c>
+      <c r="B377">
+        <v>376</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377" t="s">
+        <v>761</v>
+      </c>
+      <c r="E377" t="s">
+        <v>769</v>
+      </c>
+      <c r="F377" t="s">
+        <v>768</v>
+      </c>
+      <c r="G377">
+        <v>600</v>
+      </c>
+      <c r="H377" t="s">
+        <v>11</v>
+      </c>
+      <c r="I377" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image376.jpg</v>
+      </c>
+      <c r="M377" t="s">
+        <v>82</v>
+      </c>
+      <c r="N377" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>784</v>
+      </c>
+      <c r="B378">
+        <v>377</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378" t="s">
+        <v>761</v>
+      </c>
+      <c r="E378" t="s">
+        <v>790</v>
+      </c>
+      <c r="F378" t="s">
+        <v>99</v>
+      </c>
+      <c r="G378">
+        <v>275</v>
+      </c>
+      <c r="H378" t="s">
+        <v>11</v>
+      </c>
+      <c r="I378" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image377.jpg</v>
+      </c>
+      <c r="M378" t="s">
+        <v>82</v>
+      </c>
+      <c r="N378" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>787</v>
+      </c>
+      <c r="B379">
+        <v>378</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379" t="s">
+        <v>6</v>
+      </c>
+      <c r="E379" t="s">
+        <v>791</v>
+      </c>
+      <c r="F379" t="s">
+        <v>31</v>
+      </c>
+      <c r="G379">
+        <v>9200</v>
+      </c>
+      <c r="H379" t="s">
+        <v>11</v>
+      </c>
+      <c r="I379" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image378.jpg</v>
+      </c>
+      <c r="M379" t="s">
+        <v>82</v>
+      </c>
+      <c r="N379" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>788</v>
+      </c>
+      <c r="B380">
+        <v>379</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380" t="s">
+        <v>6</v>
+      </c>
+      <c r="E380" t="s">
+        <v>792</v>
+      </c>
+      <c r="F380" t="s">
+        <v>469</v>
+      </c>
+      <c r="G380">
+        <v>1110</v>
+      </c>
+      <c r="H380" t="s">
+        <v>11</v>
+      </c>
+      <c r="I380" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image379.jpg</v>
+      </c>
+      <c r="M380" t="s">
+        <v>82</v>
+      </c>
+      <c r="N380" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="381" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>789</v>
+      </c>
+      <c r="B381">
+        <v>380</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381" t="s">
+        <v>8</v>
+      </c>
+      <c r="E381" t="s">
+        <v>793</v>
+      </c>
+      <c r="F381" t="s">
+        <v>43</v>
+      </c>
+      <c r="G381">
+        <v>100</v>
+      </c>
+      <c r="H381" t="s">
+        <v>11</v>
+      </c>
+      <c r="I381" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image380.jpg</v>
+      </c>
+      <c r="M381" t="s">
+        <v>82</v>
+      </c>
+      <c r="N381" t="s">
         <v>101</v>
       </c>
     </row>

--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Berni\Desktop\coleccion-tarjetas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8208B2-0D90-4790-A547-649BA2B445C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005363F6-9616-49DB-AF6C-22DFF29E51E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="49845" yWindow="135" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
   </bookViews>
@@ -6513,7 +6513,7 @@
         <v>110</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111" t="s">
         <v>8</v>

--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Berni\Desktop\coleccion-tarjetas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005363F6-9616-49DB-AF6C-22DFF29E51E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C435D68A-D688-4302-B2B3-7504FE96B2B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="49845" yWindow="135" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="794">
   <si>
     <t>id</t>
   </si>
@@ -5009,6 +5009,9 @@
       <c r="G61">
         <v>69</v>
       </c>
+      <c r="H61" t="s">
+        <v>11</v>
+      </c>
       <c r="I61" t="str">
         <f t="shared" si="4"/>
         <v>/cards/image60.jpg</v>
@@ -10807,6 +10810,9 @@
       </c>
       <c r="G251">
         <v>69</v>
+      </c>
+      <c r="H251" t="s">
+        <v>11</v>
       </c>
       <c r="I251" t="str">
         <f t="shared" si="7"/>

--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Berni\Desktop\coleccion-tarjetas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD02DF6C-881B-41C6-BBE5-C470B3F2BB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80626F16-889E-410F-B662-6B46F283F410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="25815" windowHeight="20985" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -3511,7 +3511,7 @@
         <v>/cards/alt-image16.jpg</v>
       </c>
       <c r="M17" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="N17" t="s">
         <v>81</v>

--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Berni\Desktop\coleccion-tarjetas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80626F16-889E-410F-B662-6B46F283F410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD58DD5B-52F2-4E7E-A288-B7F82FD20F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="25815" windowHeight="20985" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="829">
   <si>
     <t>id</t>
   </si>
@@ -2445,6 +2445,84 @@
   </si>
   <si>
     <t>argentina</t>
+  </si>
+  <si>
+    <t>Card-385</t>
+  </si>
+  <si>
+    <t>Card-386</t>
+  </si>
+  <si>
+    <t>Card-387</t>
+  </si>
+  <si>
+    <t>Card-388</t>
+  </si>
+  <si>
+    <t>Card-389</t>
+  </si>
+  <si>
+    <t>Card-390</t>
+  </si>
+  <si>
+    <t>Card-391</t>
+  </si>
+  <si>
+    <t>Card-392</t>
+  </si>
+  <si>
+    <t>Card-393</t>
+  </si>
+  <si>
+    <t>Card-394</t>
+  </si>
+  <si>
+    <t>Card-395</t>
+  </si>
+  <si>
+    <t>pokemon</t>
+  </si>
+  <si>
+    <t>Shiny Rare</t>
+  </si>
+  <si>
+    <t>Holo</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Toxtricity Mega Evolution Phantasmal Flames #068</t>
+  </si>
+  <si>
+    <t>2023 Pokemon Abra Scarlet &amp; Violet - Paldean Fates #148</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Mega Evolution Tangela #006</t>
+  </si>
+  <si>
+    <t>Reverse Foil</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Ethan's Quilava SV: Destined Rivals #033</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Hop's Cramorant SV: Journey Together #138</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Abomasnow SV: Destined Rivals #06</t>
+  </si>
+  <si>
+    <t>2024 Pokemon Gastrodon SV08: Surging Sparks #107</t>
+  </si>
+  <si>
+    <t>2024 Pokemon Quaquaval  SV08: Surging Sparks #52</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Dawn Trainer Mega Evolution Phantasmal Flames #087</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Yveltal Mega Evolution #088</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Darumaka Mega Evolution Phantasmal Flames #015</t>
   </si>
 </sst>
 </file>
@@ -2822,7 +2900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DAA126C-D60B-4EC0-8FDE-28B90D0445C8}">
-  <dimension ref="A1:N385"/>
+  <dimension ref="A1:Q396"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="36.140625" customWidth="1"/>
@@ -3480,7 +3558,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -3517,7 +3595,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -3557,7 +3635,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>56</v>
       </c>
@@ -3597,7 +3675,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -3637,7 +3715,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -3677,7 +3755,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -3717,7 +3795,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -3757,7 +3835,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -3794,7 +3872,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -3831,7 +3909,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -3868,7 +3946,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -3905,7 +3983,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -3942,7 +4020,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -3978,8 +4056,12 @@
       <c r="N29" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q29">
+        <f>600*3888</f>
+        <v>2332800</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -4016,7 +4098,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -4056,7 +4138,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -15342,7 +15424,7 @@
         <v>480</v>
       </c>
       <c r="I363" t="str">
-        <f t="shared" ref="I363:I385" si="12">"/cards/image"&amp;ROW()-1&amp;".jpg"</f>
+        <f t="shared" ref="I363:I404" si="12">"/cards/image"&amp;ROW()-1&amp;".jpg"</f>
         <v>/cards/image362.jpg</v>
       </c>
       <c r="J363" t="str">
@@ -16154,6 +16236,369 @@
         <v>794</v>
       </c>
       <c r="N385" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>803</v>
+      </c>
+      <c r="B386">
+        <v>385</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386" t="s">
+        <v>814</v>
+      </c>
+      <c r="E386" t="s">
+        <v>818</v>
+      </c>
+      <c r="F386" t="s">
+        <v>815</v>
+      </c>
+      <c r="G386">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I386" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image385.jpg</v>
+      </c>
+      <c r="M386" t="s">
+        <v>794</v>
+      </c>
+      <c r="N386" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="387" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>804</v>
+      </c>
+      <c r="B387">
+        <v>386</v>
+      </c>
+      <c r="C387">
+        <v>1</v>
+      </c>
+      <c r="D387" t="s">
+        <v>814</v>
+      </c>
+      <c r="E387" t="s">
+        <v>817</v>
+      </c>
+      <c r="F387" t="s">
+        <v>816</v>
+      </c>
+      <c r="G387">
+        <v>4.8</v>
+      </c>
+      <c r="I387" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image386.jpg</v>
+      </c>
+      <c r="M387" t="s">
+        <v>794</v>
+      </c>
+      <c r="N387" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>805</v>
+      </c>
+      <c r="B388">
+        <v>387</v>
+      </c>
+      <c r="C388">
+        <v>1</v>
+      </c>
+      <c r="D388" t="s">
+        <v>814</v>
+      </c>
+      <c r="E388" t="s">
+        <v>819</v>
+      </c>
+      <c r="F388" t="s">
+        <v>820</v>
+      </c>
+      <c r="G388">
+        <v>4.8</v>
+      </c>
+      <c r="I388" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image387.jpg</v>
+      </c>
+      <c r="M388" t="s">
+        <v>794</v>
+      </c>
+      <c r="N388" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>806</v>
+      </c>
+      <c r="B389">
+        <v>388</v>
+      </c>
+      <c r="C389">
+        <v>1</v>
+      </c>
+      <c r="D389" t="s">
+        <v>814</v>
+      </c>
+      <c r="E389" t="s">
+        <v>821</v>
+      </c>
+      <c r="F389" t="s">
+        <v>820</v>
+      </c>
+      <c r="G389">
+        <v>4.5</v>
+      </c>
+      <c r="I389" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image388.jpg</v>
+      </c>
+      <c r="M389" t="s">
+        <v>794</v>
+      </c>
+      <c r="N389" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>807</v>
+      </c>
+      <c r="B390">
+        <v>389</v>
+      </c>
+      <c r="C390">
+        <v>1</v>
+      </c>
+      <c r="D390" t="s">
+        <v>814</v>
+      </c>
+      <c r="E390" t="s">
+        <v>822</v>
+      </c>
+      <c r="F390" t="s">
+        <v>820</v>
+      </c>
+      <c r="G390">
+        <v>4</v>
+      </c>
+      <c r="I390" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image389.jpg</v>
+      </c>
+      <c r="M390" t="s">
+        <v>794</v>
+      </c>
+      <c r="N390" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>808</v>
+      </c>
+      <c r="B391">
+        <v>390</v>
+      </c>
+      <c r="C391">
+        <v>1</v>
+      </c>
+      <c r="D391" t="s">
+        <v>814</v>
+      </c>
+      <c r="E391" t="s">
+        <v>823</v>
+      </c>
+      <c r="F391" t="s">
+        <v>820</v>
+      </c>
+      <c r="G391">
+        <v>3.5</v>
+      </c>
+      <c r="I391" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image390.jpg</v>
+      </c>
+      <c r="M391" t="s">
+        <v>794</v>
+      </c>
+      <c r="N391" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>809</v>
+      </c>
+      <c r="B392">
+        <v>391</v>
+      </c>
+      <c r="C392">
+        <v>1</v>
+      </c>
+      <c r="D392" t="s">
+        <v>814</v>
+      </c>
+      <c r="E392" t="s">
+        <v>824</v>
+      </c>
+      <c r="F392" t="s">
+        <v>820</v>
+      </c>
+      <c r="G392">
+        <v>3.5</v>
+      </c>
+      <c r="I392" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image391.jpg</v>
+      </c>
+      <c r="M392" t="s">
+        <v>794</v>
+      </c>
+      <c r="N392" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>810</v>
+      </c>
+      <c r="B393">
+        <v>392</v>
+      </c>
+      <c r="C393">
+        <v>1</v>
+      </c>
+      <c r="D393" t="s">
+        <v>814</v>
+      </c>
+      <c r="E393" t="s">
+        <v>825</v>
+      </c>
+      <c r="F393" t="s">
+        <v>820</v>
+      </c>
+      <c r="G393">
+        <v>3</v>
+      </c>
+      <c r="I393" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image392.jpg</v>
+      </c>
+      <c r="M393" t="s">
+        <v>794</v>
+      </c>
+      <c r="N393" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>811</v>
+      </c>
+      <c r="B394">
+        <v>393</v>
+      </c>
+      <c r="C394">
+        <v>1</v>
+      </c>
+      <c r="D394" t="s">
+        <v>814</v>
+      </c>
+      <c r="E394" t="s">
+        <v>826</v>
+      </c>
+      <c r="F394" t="s">
+        <v>820</v>
+      </c>
+      <c r="G394">
+        <v>2.85</v>
+      </c>
+      <c r="I394" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image393.jpg</v>
+      </c>
+      <c r="M394" t="s">
+        <v>794</v>
+      </c>
+      <c r="N394" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>812</v>
+      </c>
+      <c r="B395">
+        <v>394</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+      <c r="D395" t="s">
+        <v>814</v>
+      </c>
+      <c r="E395" t="s">
+        <v>827</v>
+      </c>
+      <c r="F395" t="s">
+        <v>816</v>
+      </c>
+      <c r="G395">
+        <v>2.75</v>
+      </c>
+      <c r="I395" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image394.jpg</v>
+      </c>
+      <c r="M395" t="s">
+        <v>794</v>
+      </c>
+      <c r="N395" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>813</v>
+      </c>
+      <c r="B396">
+        <v>395</v>
+      </c>
+      <c r="C396">
+        <v>1</v>
+      </c>
+      <c r="D396" t="s">
+        <v>814</v>
+      </c>
+      <c r="E396" t="s">
+        <v>828</v>
+      </c>
+      <c r="F396" t="s">
+        <v>820</v>
+      </c>
+      <c r="G396">
+        <v>2.5</v>
+      </c>
+      <c r="I396" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image395.jpg</v>
+      </c>
+      <c r="M396" t="s">
+        <v>794</v>
+      </c>
+      <c r="N396" t="s">
         <v>81</v>
       </c>
     </row>

--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Berni\Desktop\coleccion-tarjetas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD58DD5B-52F2-4E7E-A288-B7F82FD20F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D512238-4A17-4510-AEFA-188BEE4A36F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="25815" windowHeight="20985" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="26955" windowHeight="18840" xr2:uid="{5A110E44-25D7-4ED3-A795-D10E7F39A1FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2583" uniqueCount="865">
   <si>
     <t>id</t>
   </si>
@@ -2523,13 +2523,121 @@
   </si>
   <si>
     <t>2025 Pokemon Darumaka Mega Evolution Phantasmal Flames #015</t>
+  </si>
+  <si>
+    <t>Card-396</t>
+  </si>
+  <si>
+    <t>Card-397</t>
+  </si>
+  <si>
+    <t>Card-398</t>
+  </si>
+  <si>
+    <t>Card-399</t>
+  </si>
+  <si>
+    <t>Card-400</t>
+  </si>
+  <si>
+    <t>Card-401</t>
+  </si>
+  <si>
+    <t>Card-402</t>
+  </si>
+  <si>
+    <t>Card-403</t>
+  </si>
+  <si>
+    <t>Card-404</t>
+  </si>
+  <si>
+    <t>Card-405</t>
+  </si>
+  <si>
+    <t>Card-406</t>
+  </si>
+  <si>
+    <t>Card-407</t>
+  </si>
+  <si>
+    <t>Card-408</t>
+  </si>
+  <si>
+    <t>Card-409</t>
+  </si>
+  <si>
+    <t>Card-410</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Rapidash SV: Destined Rivals (DRI)#189</t>
+  </si>
+  <si>
+    <t>Illustration Rare</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Ethan's Adventure Trainer SV: Destined Rivals (DRI) 221</t>
+  </si>
+  <si>
+    <t>Ultra Rare</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Blaziken SV: Destined Rivals (DRI) #192</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Zacian Mega Evolution Phantasmal Flames [PFL] #100</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Snover Mega Evolution [MEG] #140</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Night Stretcher Mega Evolution [MEG] #173</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Mega Evolution [MEG] - #086</t>
+  </si>
+  <si>
+    <t>Double Rare</t>
+  </si>
+  <si>
+    <t>2025 Pokemon Mega Evolution IR Ivysaur #134 CGC 10 GEM MINT</t>
+  </si>
+  <si>
+    <t>2024 Pokemon Scarlet &amp; Violet Surging Sparks Latios #203 PSA 9 MINT</t>
+  </si>
+  <si>
+    <t>2021 Pokemon Sword &amp; Shield Evolving Skies Umbreon V #94 PSA 9 MINT</t>
+  </si>
+  <si>
+    <t>2024 Pokemon Scarlet &amp; Violet Temporal Forces SIR Walking Wake EX #205 CGC 10 GEM MINT</t>
+  </si>
+  <si>
+    <t>Special Illustration Rare</t>
+  </si>
+  <si>
+    <t>2013 Pokemon Black &amp; White Legendary Treasures Gold Rare Reshiram #114 PSA 6 EXMT</t>
+  </si>
+  <si>
+    <t>Secret Rare</t>
+  </si>
+  <si>
+    <t>2018 Pokemon Sun &amp; Moon Ultra Prism Rainbow Rare Palkia GX #165 CGC 8.5 NM-MT+</t>
+  </si>
+  <si>
+    <t>Ultra Prism</t>
+  </si>
+  <si>
+    <t>2025 Pokemon SV Destined Rivals IR Arven's Greedent #205 CGC 9 MINT</t>
+  </si>
+  <si>
+    <t>2025 Pokemon SV Destined Rivals Full Art Team Rocket's Nidoking ex #216 CGC 9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2542,6 +2650,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF444444"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2564,8 +2678,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2900,7 +3015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DAA126C-D60B-4EC0-8FDE-28B90D0445C8}">
-  <dimension ref="A1:Q396"/>
+  <dimension ref="A1:Q411"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="36.140625" customWidth="1"/>
@@ -4109,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>757</v>
       </c>
       <c r="E31" t="s">
         <v>97</v>
@@ -4223,7 +4338,7 @@
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>6</v>
+        <v>757</v>
       </c>
       <c r="E34" t="s">
         <v>101</v>
@@ -4445,7 +4560,7 @@
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>6</v>
+        <v>757</v>
       </c>
       <c r="E40" t="s">
         <v>109</v>
@@ -15424,7 +15539,7 @@
         <v>480</v>
       </c>
       <c r="I363" t="str">
-        <f t="shared" ref="I363:I404" si="12">"/cards/image"&amp;ROW()-1&amp;".jpg"</f>
+        <f t="shared" ref="I363:I411" si="12">"/cards/image"&amp;ROW()-1&amp;".jpg"</f>
         <v>/cards/image362.jpg</v>
       </c>
       <c r="J363" t="str">
@@ -16599,6 +16714,501 @@
         <v>794</v>
       </c>
       <c r="N396" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>829</v>
+      </c>
+      <c r="B397">
+        <v>396</v>
+      </c>
+      <c r="C397">
+        <v>1</v>
+      </c>
+      <c r="D397" t="s">
+        <v>814</v>
+      </c>
+      <c r="E397" t="s">
+        <v>844</v>
+      </c>
+      <c r="F397" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="G397">
+        <v>15</v>
+      </c>
+      <c r="I397" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image396.jpg</v>
+      </c>
+      <c r="M397" t="s">
+        <v>794</v>
+      </c>
+      <c r="N397" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>830</v>
+      </c>
+      <c r="B398">
+        <v>397</v>
+      </c>
+      <c r="C398">
+        <v>1</v>
+      </c>
+      <c r="D398" t="s">
+        <v>814</v>
+      </c>
+      <c r="E398" t="s">
+        <v>846</v>
+      </c>
+      <c r="F398" t="s">
+        <v>847</v>
+      </c>
+      <c r="G398">
+        <v>3.5</v>
+      </c>
+      <c r="I398" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image397.jpg</v>
+      </c>
+      <c r="M398" t="s">
+        <v>794</v>
+      </c>
+      <c r="N398" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>831</v>
+      </c>
+      <c r="B399">
+        <v>398</v>
+      </c>
+      <c r="C399">
+        <v>1</v>
+      </c>
+      <c r="D399" t="s">
+        <v>814</v>
+      </c>
+      <c r="E399" t="s">
+        <v>848</v>
+      </c>
+      <c r="F399" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="G399">
+        <v>20</v>
+      </c>
+      <c r="I399" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image398.jpg</v>
+      </c>
+      <c r="M399" t="s">
+        <v>794</v>
+      </c>
+      <c r="N399" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>832</v>
+      </c>
+      <c r="B400">
+        <v>399</v>
+      </c>
+      <c r="C400">
+        <v>1</v>
+      </c>
+      <c r="D400" t="s">
+        <v>814</v>
+      </c>
+      <c r="E400" t="s">
+        <v>849</v>
+      </c>
+      <c r="F400" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="G400">
+        <v>12</v>
+      </c>
+      <c r="I400" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image399.jpg</v>
+      </c>
+      <c r="M400" t="s">
+        <v>794</v>
+      </c>
+      <c r="N400" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>833</v>
+      </c>
+      <c r="B401">
+        <v>400</v>
+      </c>
+      <c r="C401">
+        <v>1</v>
+      </c>
+      <c r="D401" t="s">
+        <v>814</v>
+      </c>
+      <c r="E401" t="s">
+        <v>850</v>
+      </c>
+      <c r="F401" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="G401">
+        <v>5</v>
+      </c>
+      <c r="I401" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image400.jpg</v>
+      </c>
+      <c r="M401" t="s">
+        <v>794</v>
+      </c>
+      <c r="N401" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>834</v>
+      </c>
+      <c r="B402">
+        <v>401</v>
+      </c>
+      <c r="C402">
+        <v>1</v>
+      </c>
+      <c r="D402" t="s">
+        <v>814</v>
+      </c>
+      <c r="E402" t="s">
+        <v>851</v>
+      </c>
+      <c r="F402" t="s">
+        <v>847</v>
+      </c>
+      <c r="G402">
+        <v>5.5</v>
+      </c>
+      <c r="I402" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image401.jpg</v>
+      </c>
+      <c r="M402" t="s">
+        <v>794</v>
+      </c>
+      <c r="N402" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>835</v>
+      </c>
+      <c r="B403">
+        <v>402</v>
+      </c>
+      <c r="C403">
+        <v>1</v>
+      </c>
+      <c r="D403" t="s">
+        <v>814</v>
+      </c>
+      <c r="E403" t="s">
+        <v>852</v>
+      </c>
+      <c r="F403" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="G403">
+        <v>2</v>
+      </c>
+      <c r="I403" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image402.jpg</v>
+      </c>
+      <c r="M403" t="s">
+        <v>794</v>
+      </c>
+      <c r="N403" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>836</v>
+      </c>
+      <c r="B404">
+        <v>403</v>
+      </c>
+      <c r="C404">
+        <v>1</v>
+      </c>
+      <c r="D404" t="s">
+        <v>814</v>
+      </c>
+      <c r="E404" t="s">
+        <v>854</v>
+      </c>
+      <c r="F404" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="G404">
+        <v>65</v>
+      </c>
+      <c r="I404" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image403.jpg</v>
+      </c>
+      <c r="M404" t="s">
+        <v>801</v>
+      </c>
+      <c r="N404" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>837</v>
+      </c>
+      <c r="B405">
+        <v>404</v>
+      </c>
+      <c r="C405">
+        <v>1</v>
+      </c>
+      <c r="D405" t="s">
+        <v>814</v>
+      </c>
+      <c r="E405" t="s">
+        <v>855</v>
+      </c>
+      <c r="F405" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="G405">
+        <v>59</v>
+      </c>
+      <c r="I405" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image404.jpg</v>
+      </c>
+      <c r="M405" t="s">
+        <v>801</v>
+      </c>
+      <c r="N405" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="406" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>838</v>
+      </c>
+      <c r="B406">
+        <v>405</v>
+      </c>
+      <c r="C406">
+        <v>1</v>
+      </c>
+      <c r="D406" t="s">
+        <v>814</v>
+      </c>
+      <c r="E406" t="s">
+        <v>856</v>
+      </c>
+      <c r="F406" t="s">
+        <v>847</v>
+      </c>
+      <c r="G406">
+        <v>35</v>
+      </c>
+      <c r="I406" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image405.jpg</v>
+      </c>
+      <c r="M406" t="s">
+        <v>801</v>
+      </c>
+      <c r="N406" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="407" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>839</v>
+      </c>
+      <c r="B407">
+        <v>406</v>
+      </c>
+      <c r="C407">
+        <v>1</v>
+      </c>
+      <c r="D407" t="s">
+        <v>814</v>
+      </c>
+      <c r="E407" t="s">
+        <v>857</v>
+      </c>
+      <c r="F407" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="G407">
+        <v>85</v>
+      </c>
+      <c r="I407" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image406.jpg</v>
+      </c>
+      <c r="M407" t="s">
+        <v>801</v>
+      </c>
+      <c r="N407" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="408" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>840</v>
+      </c>
+      <c r="B408">
+        <v>407</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+      <c r="D408" t="s">
+        <v>814</v>
+      </c>
+      <c r="E408" t="s">
+        <v>859</v>
+      </c>
+      <c r="F408" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="G408">
+        <v>300</v>
+      </c>
+      <c r="I408" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image407.jpg</v>
+      </c>
+      <c r="M408" t="s">
+        <v>801</v>
+      </c>
+      <c r="N408" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="409" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>841</v>
+      </c>
+      <c r="B409">
+        <v>408</v>
+      </c>
+      <c r="C409">
+        <v>1</v>
+      </c>
+      <c r="D409" t="s">
+        <v>814</v>
+      </c>
+      <c r="E409" t="s">
+        <v>861</v>
+      </c>
+      <c r="F409" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="G409">
+        <v>65</v>
+      </c>
+      <c r="I409" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image408.jpg</v>
+      </c>
+      <c r="M409" t="s">
+        <v>801</v>
+      </c>
+      <c r="N409" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="410" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>842</v>
+      </c>
+      <c r="B410">
+        <v>409</v>
+      </c>
+      <c r="C410">
+        <v>1</v>
+      </c>
+      <c r="D410" t="s">
+        <v>814</v>
+      </c>
+      <c r="E410" t="s">
+        <v>863</v>
+      </c>
+      <c r="F410" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="G410">
+        <v>19</v>
+      </c>
+      <c r="I410" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image409.jpg</v>
+      </c>
+      <c r="M410" t="s">
+        <v>801</v>
+      </c>
+      <c r="N410" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="411" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>843</v>
+      </c>
+      <c r="B411">
+        <v>410</v>
+      </c>
+      <c r="C411">
+        <v>1</v>
+      </c>
+      <c r="D411" t="s">
+        <v>814</v>
+      </c>
+      <c r="E411" t="s">
+        <v>864</v>
+      </c>
+      <c r="F411" t="s">
+        <v>847</v>
+      </c>
+      <c r="G411">
+        <v>24</v>
+      </c>
+      <c r="I411" t="str">
+        <f t="shared" si="12"/>
+        <v>/cards/image410.jpg</v>
+      </c>
+      <c r="M411" t="s">
+        <v>801</v>
+      </c>
+      <c r="N411" t="s">
         <v>81</v>
       </c>
     </row>
